--- a/ARM Functions/Ability Edits/Intimidate, Inner Focus, Own Tempo, Oblivious, Rattled.xlsx
+++ b/ARM Functions/Ability Edits/Intimidate, Inner Focus, Own Tempo, Oblivious, Rattled.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Ability Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9310190F-1932-4D93-BDB3-C4C5C0EC9AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDE1C6B-8E4A-403A-A0A9-D852EC4E053F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
+    <workbookView xWindow="-16466" yWindow="0" windowWidth="16466" windowHeight="17914" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="edit" sheetId="13" r:id="rId1"/>
@@ -5071,7 +5071,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5083,14 +5083,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Cambria"/>
-      <family val="1"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Cambria"/>
-      <family val="1"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="9">
@@ -5155,29 +5155,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -5514,19 +5512,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49E4E9E0-357D-4159-9AD8-09B8F8CC188E}">
   <dimension ref="A1:D125"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.0703125" defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="12" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.53125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.73046875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.1328125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="13.59765625" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9.06640625" style="3"/>
+    <col min="2" max="2" width="9.35546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.35546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9.0703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5540,7 +5538,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>1558</v>
       </c>
@@ -5548,7 +5546,7 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
         <v>1561</v>
       </c>
@@ -5561,7 +5559,7 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4">
       <c r="A4" s="3" t="str">
         <f t="shared" ref="A4:A6" si="0">DEC2HEX(HEX2DEC(A3)+4,8)</f>
         <v>000D6E50</v>
@@ -5574,7 +5572,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4">
       <c r="A5" s="3" t="str">
         <f t="shared" si="0"/>
         <v>000D6E54</v>
@@ -5587,7 +5585,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4">
       <c r="A6" s="3" t="str">
         <f t="shared" si="0"/>
         <v>000D6E58</v>
@@ -5600,7 +5598,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4">
       <c r="A7" s="3" t="str">
         <f>DEC2HEX(HEX2DEC(A6)+4,8)</f>
         <v>000D6E5C</v>
@@ -5613,323 +5611,323 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:4">
+      <c r="A9" s="5" t="s">
         <v>1555</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10" s="6" t="s">
         <v>1562</v>
       </c>
-      <c r="B10" s="5" t="str">
+      <c r="B10" s="7" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(C10,1),"10A0E3")</f>
         <v>0310A0E3</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="7" t="s">
         <v>1582</v>
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="str">
+    <row r="11" spans="1:4">
+      <c r="A11" s="7" t="str">
         <f t="shared" ref="A11:A13" si="1">DEC2HEX(HEX2DEC(A10)+4,8)</f>
         <v>000DAB48</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="6" t="s">
         <v>837</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="7" t="s">
         <v>833</v>
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="str">
+    <row r="12" spans="1:4">
+      <c r="A12" s="7" t="str">
         <f t="shared" si="1"/>
         <v>000DAB4C</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>838</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="7" t="s">
         <v>835</v>
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="str">
+    <row r="13" spans="1:4">
+      <c r="A13" s="7" t="str">
         <f t="shared" si="1"/>
         <v>000DAB50</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="7" t="s">
         <v>839</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="7" t="s">
         <v>834</v>
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="str">
+    <row r="14" spans="1:4">
+      <c r="A14" s="7" t="str">
         <f>DEC2HEX(HEX2DEC(A13)+4,8)</f>
         <v>000DAB54</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="6" t="s">
         <v>832</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="7" t="s">
         <v>836</v>
       </c>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
+    <row r="15" spans="1:4">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="5" t="s">
         <v>1556</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+    <row r="17" spans="1:4">
+      <c r="A17" s="6" t="s">
         <v>1563</v>
       </c>
-      <c r="B17" s="5" t="str">
+      <c r="B17" s="7" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(C17,1),"10A0E3")</f>
         <v>0610A0E3</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="7" t="s">
         <v>1661</v>
       </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="str">
+    <row r="18" spans="1:4">
+      <c r="A18" s="7" t="str">
         <f t="shared" ref="A18:A20" si="2">DEC2HEX(HEX2DEC(A17)+4,8)</f>
         <v>000D792C</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="6" t="s">
         <v>837</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="7" t="s">
         <v>833</v>
       </c>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="str">
+    <row r="19" spans="1:4">
+      <c r="A19" s="7" t="str">
         <f t="shared" si="2"/>
         <v>000D7930</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="7" t="s">
         <v>838</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="7" t="s">
         <v>835</v>
       </c>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="5" t="str">
+    <row r="20" spans="1:4">
+      <c r="A20" s="7" t="str">
         <f t="shared" si="2"/>
         <v>000D7934</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="7" t="s">
         <v>839</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="7" t="s">
         <v>834</v>
       </c>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="str">
+    <row r="21" spans="1:4">
+      <c r="A21" s="7" t="str">
         <f>DEC2HEX(HEX2DEC(A20)+4,8)</f>
         <v>000D7938</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="6" t="s">
         <v>832</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="7" t="s">
         <v>836</v>
       </c>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
+    <row r="22" spans="1:4">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="5" t="s">
         <v>1557</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="10" t="s">
+    <row r="24" spans="1:4">
+      <c r="A24" s="6" t="s">
         <v>1564</v>
       </c>
-      <c r="B24" s="5" t="str">
+      <c r="B24" s="7" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(C24,1),"10A0E3")</f>
         <v>0710A0E3</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="7" t="s">
         <v>1581</v>
       </c>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="5" t="str">
+    <row r="25" spans="1:4">
+      <c r="A25" s="7" t="str">
         <f t="shared" ref="A25:A27" si="3">DEC2HEX(HEX2DEC(A24)+4,8)</f>
         <v>000D7850</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="6" t="s">
         <v>837</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="7" t="s">
         <v>833</v>
       </c>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="5" t="str">
+    <row r="26" spans="1:4">
+      <c r="A26" s="7" t="str">
         <f t="shared" si="3"/>
         <v>000D7854</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="7" t="s">
         <v>838</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="7" t="s">
         <v>835</v>
       </c>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="5" t="str">
+    <row r="27" spans="1:4">
+      <c r="A27" s="7" t="str">
         <f t="shared" si="3"/>
         <v>000D7858</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="7" t="s">
         <v>839</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="7" t="s">
         <v>834</v>
       </c>
       <c r="D27" s="2"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="5" t="str">
+    <row r="28" spans="1:4">
+      <c r="A28" s="7" t="str">
         <f>DEC2HEX(HEX2DEC(A27)+4,8)</f>
         <v>000D785C</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="6" t="s">
         <v>832</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="7" t="s">
         <v>836</v>
       </c>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="12" t="s">
+    <row r="29" spans="1:4">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="9" t="s">
         <v>1559</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="9" t="s">
+    <row r="31" spans="1:4">
+      <c r="A31" s="10" t="s">
         <v>1565</v>
       </c>
-      <c r="B31" s="7" t="str">
+      <c r="B31" s="8" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(C31,1),"10A0E3")</f>
         <v>0210A0E3</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="8" t="s">
         <v>1560</v>
       </c>
       <c r="D31" s="2"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="7" t="str">
+    <row r="32" spans="1:4">
+      <c r="A32" s="8" t="str">
         <f t="shared" ref="A32:A34" si="4">DEC2HEX(HEX2DEC(A31)+4,8)</f>
         <v>000D7814</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="10" t="s">
         <v>837</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="8" t="s">
         <v>833</v>
       </c>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="str">
+    <row r="33" spans="1:4">
+      <c r="A33" s="8" t="str">
         <f t="shared" si="4"/>
         <v>000D7818</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="8" t="s">
         <v>838</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="8" t="s">
         <v>835</v>
       </c>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="7" t="str">
+    <row r="34" spans="1:4">
+      <c r="A34" s="8" t="str">
         <f t="shared" si="4"/>
         <v>000D781C</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="8" t="s">
         <v>839</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="8" t="s">
         <v>834</v>
       </c>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="7" t="str">
+    <row r="35" spans="1:4">
+      <c r="A35" s="8" t="str">
         <f>DEC2HEX(HEX2DEC(A34)+4,8)</f>
         <v>000D7820</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="10" t="s">
         <v>832</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="8" t="s">
         <v>836</v>
       </c>
       <c r="D35" s="2"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4">
       <c r="B36" s="4"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4">
       <c r="A37" s="2" t="s">
         <v>1545</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
         <v>1566</v>
       </c>
@@ -5940,7 +5938,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4">
       <c r="A39" s="3" t="str">
         <f t="shared" ref="A39:A61" si="5">DEC2HEX(HEX2DEC(A38)+4,8)</f>
         <v>00100030</v>
@@ -5952,7 +5950,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4">
       <c r="A40" s="3" t="str">
         <f t="shared" si="5"/>
         <v>00100034</v>
@@ -5964,7 +5962,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4">
       <c r="A41" s="3" t="str">
         <f t="shared" si="5"/>
         <v>00100038</v>
@@ -5976,271 +5974,271 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="5" t="str">
+    <row r="42" spans="1:4">
+      <c r="A42" s="7" t="str">
         <f t="shared" si="5"/>
         <v>0010003C</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="7" t="s">
         <v>1571</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="7" t="s">
         <v>1544</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="7" t="s">
         <v>1597</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="5" t="str">
+    <row r="43" spans="1:4">
+      <c r="A43" s="7" t="str">
         <f t="shared" si="5"/>
         <v>00100040</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="7" t="s">
         <v>1627</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="7" t="s">
         <v>1543</v>
       </c>
-      <c r="D43" s="5"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="str">
+      <c r="D43" s="7"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="7" t="str">
         <f t="shared" si="5"/>
         <v>00100044</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="6" t="s">
         <v>1572</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="7" t="s">
         <v>830</v>
       </c>
-      <c r="D44" s="5"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="5" t="str">
+      <c r="D44" s="7"/>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="7" t="str">
         <f t="shared" si="5"/>
         <v>00100048</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="7" t="s">
         <v>1628</v>
       </c>
-      <c r="C45" s="5" t="str">
+      <c r="C45" s="7" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$61)</f>
         <v>bne 0x00100088</v>
       </c>
-      <c r="D45" s="5"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="13" t="str">
+      <c r="D45" s="7"/>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="11" t="str">
         <f t="shared" si="5"/>
         <v>0010004C</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="11" t="s">
         <v>1629</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="11" t="s">
         <v>1599</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="11" t="s">
         <v>1598</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="13" t="str">
+    <row r="47" spans="1:4">
+      <c r="A47" s="11" t="str">
         <f t="shared" si="5"/>
         <v>00100050</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="11" t="s">
         <v>1630</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="11" t="s">
         <v>1543</v>
       </c>
-      <c r="D47" s="13"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="13" t="str">
+      <c r="D47" s="11"/>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="11" t="str">
         <f t="shared" si="5"/>
         <v>00100054</v>
       </c>
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="12" t="s">
         <v>1573</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="C48" s="11" t="s">
         <v>1554</v>
       </c>
-      <c r="D48" s="13"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="13" t="str">
+      <c r="D48" s="11"/>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="11" t="str">
         <f t="shared" si="5"/>
         <v>00100058</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" s="11" t="s">
         <v>1663</v>
       </c>
-      <c r="C49" s="13" t="str">
+      <c r="C49" s="11" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$61)</f>
         <v>bne 0x00100088</v>
       </c>
-      <c r="D49" s="13"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="7" t="str">
+      <c r="D49" s="11"/>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="8" t="str">
         <f t="shared" si="5"/>
         <v>0010005C</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="8" t="s">
         <v>1591</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="8" t="s">
         <v>1584</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="8" t="s">
         <v>1596</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="7" t="str">
+    <row r="51" spans="1:4">
+      <c r="A51" s="8" t="str">
         <f t="shared" si="5"/>
         <v>00100060</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="8" t="s">
         <v>1631</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="8" t="s">
         <v>1543</v>
       </c>
-      <c r="D51" s="7"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="7" t="str">
+      <c r="D51" s="8"/>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="8" t="str">
         <f t="shared" si="5"/>
         <v>00100064</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="10" t="s">
         <v>1572</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="8" t="s">
         <v>830</v>
       </c>
-      <c r="D52" s="7"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="7" t="str">
+      <c r="D52" s="8"/>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="8" t="str">
         <f t="shared" si="5"/>
         <v>00100068</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="8" t="s">
         <v>1662</v>
       </c>
-      <c r="C53" s="7" t="str">
+      <c r="C53" s="8" t="str">
         <f>_xlfn.CONCAT("beq 0x",A$61)</f>
         <v>beq 0x00100088</v>
       </c>
-      <c r="D53" s="7"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="6" t="str">
+      <c r="D53" s="8"/>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="13" t="str">
         <f t="shared" si="5"/>
         <v>0010006C</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="14" t="s">
         <v>1592</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="13" t="s">
         <v>1585</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="13" t="s">
         <v>1600</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="6" t="str">
+    <row r="55" spans="1:4">
+      <c r="A55" s="13" t="str">
         <f t="shared" si="5"/>
         <v>00100070</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="13" t="s">
         <v>1593</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="13" t="s">
         <v>1587</v>
       </c>
-      <c r="D55" s="6"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="6" t="str">
+      <c r="D55" s="13"/>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="13" t="str">
         <f t="shared" si="5"/>
         <v>00100074</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="13" t="s">
         <v>1594</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="13" t="s">
         <v>1589</v>
       </c>
-      <c r="D56" s="6"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="14" t="str">
+      <c r="D56" s="13"/>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="15" t="str">
         <f t="shared" si="5"/>
         <v>00100078</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="15" t="s">
         <v>1632</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="15" t="s">
         <v>1602</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="D57" s="15" t="s">
         <v>1601</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="14" t="str">
+    <row r="58" spans="1:4">
+      <c r="A58" s="15" t="str">
         <f t="shared" si="5"/>
         <v>0010007C</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B58" s="15" t="s">
         <v>1595</v>
       </c>
-      <c r="C58" s="14" t="s">
+      <c r="C58" s="15" t="s">
         <v>1588</v>
       </c>
-      <c r="D58" s="14"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="14" t="str">
+      <c r="D58" s="15"/>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="15" t="str">
         <f t="shared" si="5"/>
         <v>00100080</v>
       </c>
-      <c r="B59" s="15" t="s">
+      <c r="B59" s="16" t="s">
         <v>1633</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="15" t="s">
         <v>1603</v>
       </c>
-      <c r="D59" s="14" t="s">
+      <c r="D59" s="15" t="s">
         <v>1604</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="14" t="str">
+    <row r="60" spans="1:4">
+      <c r="A60" s="15" t="str">
         <f t="shared" si="5"/>
         <v>00100084</v>
       </c>
-      <c r="B60" s="15" t="s">
+      <c r="B60" s="16" t="s">
         <v>1634</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="15" t="s">
         <v>1606</v>
       </c>
-      <c r="D60" s="14" t="s">
+      <c r="D60" s="15" t="s">
         <v>1605</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4">
       <c r="A61" s="3" t="str">
         <f t="shared" si="5"/>
         <v>00100088</v>
@@ -6253,12 +6251,12 @@
         <v>pop {r4, r5, r6, pc}</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4">
       <c r="A63" s="2" t="s">
         <v>1546</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4">
       <c r="A64" s="3" t="str">
         <f>DEC2HEX(HEX2DEC(A61)+4,8)</f>
         <v>0010008C</v>
@@ -6270,7 +6268,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4">
       <c r="A65" s="3" t="str">
         <f t="shared" ref="A65:A71" si="6">DEC2HEX(HEX2DEC(A64)+4,8)</f>
         <v>00100090</v>
@@ -6282,7 +6280,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4">
       <c r="A66" s="3" t="str">
         <f t="shared" si="6"/>
         <v>00100094</v>
@@ -6298,7 +6296,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4">
       <c r="A67" s="3" t="str">
         <f t="shared" si="6"/>
         <v>00100098</v>
@@ -6310,7 +6308,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4">
       <c r="A68" s="3" t="str">
         <f t="shared" si="6"/>
         <v>0010009C</v>
@@ -6322,7 +6320,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4">
       <c r="A69" s="3" t="str">
         <f t="shared" si="6"/>
         <v>001000A0</v>
@@ -6334,7 +6332,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4">
       <c r="A70" s="3" t="str">
         <f t="shared" si="6"/>
         <v>001000A4</v>
@@ -6347,7 +6345,7 @@
         <v>pop {r3 , pc}</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4">
       <c r="A71" s="3" t="str">
         <f t="shared" si="6"/>
         <v>001000A8</v>
@@ -6359,12 +6357,12 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4">
       <c r="A73" s="2" t="s">
         <v>1583</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4">
       <c r="A74" s="3" t="str">
         <f>DEC2HEX(HEX2DEC(A71)+4,8)</f>
         <v>001000AC</v>
@@ -6376,7 +6374,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4">
       <c r="A75" s="3" t="str">
         <f t="shared" ref="A75:A95" si="7">DEC2HEX(HEX2DEC(A74)+4,8)</f>
         <v>001000B0</v>
@@ -6388,7 +6386,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4">
       <c r="A76" s="3" t="str">
         <f t="shared" si="7"/>
         <v>001000B4</v>
@@ -6400,325 +6398,325 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="5" t="str">
+    <row r="77" spans="1:4">
+      <c r="A77" s="7" t="str">
         <f t="shared" si="7"/>
         <v>001000B8</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="7" t="s">
         <v>1571</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="7" t="s">
         <v>1544</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="D77" s="7" t="s">
         <v>1597</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="5" t="str">
+    <row r="78" spans="1:4">
+      <c r="A78" s="7" t="str">
         <f t="shared" si="7"/>
         <v>001000BC</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="7" t="s">
         <v>1636</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="C78" s="7" t="s">
         <v>1543</v>
       </c>
-      <c r="D78" s="5"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="5" t="str">
+      <c r="D78" s="7"/>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="7" t="str">
         <f t="shared" si="7"/>
         <v>001000C0</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B79" s="6" t="s">
         <v>1572</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="C79" s="7" t="s">
         <v>830</v>
       </c>
-      <c r="D79" s="5"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="5" t="str">
+      <c r="D79" s="7"/>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="7" t="str">
         <f t="shared" si="7"/>
         <v>001000C4</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="B80" s="7" t="s">
         <v>1667</v>
       </c>
-      <c r="C80" s="5" t="str">
+      <c r="C80" s="7" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$125)</f>
         <v>bne 0x00100178</v>
       </c>
-      <c r="D80" s="5"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" s="13" t="str">
+      <c r="D80" s="7"/>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="11" t="str">
         <f t="shared" si="7"/>
         <v>001000C8</v>
       </c>
-      <c r="B81" s="13" t="s">
+      <c r="B81" s="11" t="s">
         <v>1629</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="11" t="s">
         <v>1599</v>
       </c>
-      <c r="D81" s="13" t="s">
+      <c r="D81" s="11" t="s">
         <v>1598</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" s="13" t="str">
+    <row r="82" spans="1:4">
+      <c r="A82" s="11" t="str">
         <f t="shared" si="7"/>
         <v>001000CC</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="B82" s="11" t="s">
         <v>1637</v>
       </c>
-      <c r="C82" s="13" t="s">
+      <c r="C82" s="11" t="s">
         <v>1543</v>
       </c>
-      <c r="D82" s="13"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" s="13" t="str">
+      <c r="D82" s="11"/>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="11" t="str">
         <f t="shared" si="7"/>
         <v>001000D0</v>
       </c>
-      <c r="B83" s="20" t="s">
+      <c r="B83" s="12" t="s">
         <v>1573</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="C83" s="11" t="s">
         <v>1554</v>
       </c>
-      <c r="D83" s="13"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" s="13" t="str">
+      <c r="D83" s="11"/>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="11" t="str">
         <f t="shared" si="7"/>
         <v>001000D4</v>
       </c>
-      <c r="B84" s="13" t="s">
+      <c r="B84" s="11" t="s">
         <v>1668</v>
       </c>
-      <c r="C84" s="13" t="str">
+      <c r="C84" s="11" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$125)</f>
         <v>bne 0x00100178</v>
       </c>
-      <c r="D84" s="13"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" s="7" t="str">
+      <c r="D84" s="11"/>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="8" t="str">
         <f t="shared" si="7"/>
         <v>001000D8</v>
       </c>
-      <c r="B85" s="7" t="s">
+      <c r="B85" s="8" t="s">
         <v>1591</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="C85" s="8" t="s">
         <v>1584</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="D85" s="8" t="s">
         <v>1596</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" s="7" t="str">
+    <row r="86" spans="1:4">
+      <c r="A86" s="8" t="str">
         <f t="shared" si="7"/>
         <v>001000DC</v>
       </c>
-      <c r="B86" s="7" t="s">
+      <c r="B86" s="8" t="s">
         <v>1638</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="C86" s="8" t="s">
         <v>1543</v>
       </c>
-      <c r="D86" s="7"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" s="7" t="str">
+      <c r="D86" s="8"/>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="8" t="str">
         <f t="shared" si="7"/>
         <v>001000E0</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" s="10" t="s">
         <v>1572</v>
       </c>
-      <c r="C87" s="7" t="s">
+      <c r="C87" s="8" t="s">
         <v>830</v>
       </c>
-      <c r="D87" s="7"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" s="7" t="str">
+      <c r="D87" s="8"/>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="8" t="str">
         <f t="shared" si="7"/>
         <v>001000E4</v>
       </c>
-      <c r="B88" s="7" t="s">
+      <c r="B88" s="8" t="s">
         <v>1669</v>
       </c>
-      <c r="C88" s="7" t="str">
+      <c r="C88" s="8" t="str">
         <f>_xlfn.CONCAT("beq 0x",A$125)</f>
         <v>beq 0x00100178</v>
       </c>
-      <c r="D88" s="7"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" s="6" t="str">
+      <c r="D88" s="8"/>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="13" t="str">
         <f t="shared" si="7"/>
         <v>001000E8</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B89" s="14" t="s">
         <v>1592</v>
       </c>
-      <c r="C89" s="6" t="s">
+      <c r="C89" s="13" t="s">
         <v>1585</v>
       </c>
-      <c r="D89" s="6" t="s">
+      <c r="D89" s="13" t="s">
         <v>1600</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" s="6" t="str">
+    <row r="90" spans="1:4">
+      <c r="A90" s="13" t="str">
         <f t="shared" si="7"/>
         <v>001000EC</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="13" t="s">
         <v>1593</v>
       </c>
-      <c r="C90" s="6" t="s">
+      <c r="C90" s="13" t="s">
         <v>1587</v>
       </c>
-      <c r="D90" s="6"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" s="6" t="str">
+      <c r="D90" s="13"/>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="13" t="str">
         <f t="shared" si="7"/>
         <v>001000F0</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="13" t="s">
         <v>1639</v>
       </c>
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="13" t="s">
         <v>1589</v>
       </c>
-      <c r="D91" s="6"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" s="14" t="str">
+      <c r="D91" s="13"/>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="15" t="str">
         <f t="shared" si="7"/>
         <v>001000F4</v>
       </c>
-      <c r="B92" s="14" t="s">
+      <c r="B92" s="15" t="s">
         <v>1632</v>
       </c>
-      <c r="C92" s="14" t="s">
+      <c r="C92" s="15" t="s">
         <v>1602</v>
       </c>
-      <c r="D92" s="14" t="s">
+      <c r="D92" s="15" t="s">
         <v>1601</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" s="14" t="str">
+    <row r="93" spans="1:4">
+      <c r="A93" s="15" t="str">
         <f t="shared" si="7"/>
         <v>001000F8</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="B93" s="15" t="s">
         <v>1640</v>
       </c>
-      <c r="C93" s="14" t="s">
+      <c r="C93" s="15" t="s">
         <v>1588</v>
       </c>
-      <c r="D93" s="14"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" s="14" t="str">
+      <c r="D93" s="15"/>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="15" t="str">
         <f t="shared" si="7"/>
         <v>001000FC</v>
       </c>
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="16" t="s">
         <v>1633</v>
       </c>
-      <c r="C94" s="14" t="s">
+      <c r="C94" s="15" t="s">
         <v>1603</v>
       </c>
-      <c r="D94" s="14" t="s">
+      <c r="D94" s="15" t="s">
         <v>1604</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" s="14" t="str">
+    <row r="95" spans="1:4">
+      <c r="A95" s="15" t="str">
         <f t="shared" si="7"/>
         <v>00100100</v>
       </c>
-      <c r="B95" s="15" t="s">
+      <c r="B95" s="16" t="s">
         <v>1670</v>
       </c>
-      <c r="C95" s="14" t="str">
+      <c r="C95" s="15" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$125)</f>
         <v>bne 0x00100178</v>
       </c>
-      <c r="D95" s="14"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" s="18" t="str">
+      <c r="D95" s="15"/>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="17" t="str">
         <f t="shared" ref="A96:A125" si="8">DEC2HEX(HEX2DEC(A95)+4,8)</f>
         <v>00100104</v>
       </c>
-      <c r="B96" s="18" t="s">
+      <c r="B96" s="17" t="s">
         <v>1641</v>
       </c>
-      <c r="C96" s="18" t="s">
+      <c r="C96" s="17" t="s">
         <v>1607</v>
       </c>
-      <c r="D96" s="18" t="s">
+      <c r="D96" s="17" t="s">
         <v>1609</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" s="18" t="str">
+    <row r="97" spans="1:4">
+      <c r="A97" s="17" t="str">
         <f t="shared" si="8"/>
         <v>00100108</v>
       </c>
-      <c r="B97" s="18" t="s">
+      <c r="B97" s="17" t="s">
         <v>1642</v>
       </c>
-      <c r="C97" s="18" t="s">
+      <c r="C97" s="17" t="s">
         <v>1543</v>
       </c>
-      <c r="D97" s="18"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" s="18" t="str">
+      <c r="D97" s="17"/>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="17" t="str">
         <f t="shared" si="8"/>
         <v>0010010C</v>
       </c>
-      <c r="B98" s="21" t="s">
+      <c r="B98" s="18" t="s">
         <v>1643</v>
       </c>
-      <c r="C98" s="18" t="s">
+      <c r="C98" s="17" t="s">
         <v>1608</v>
       </c>
-      <c r="D98" s="18"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" s="18" t="str">
+      <c r="D98" s="17"/>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="17" t="str">
         <f t="shared" si="8"/>
         <v>00100110</v>
       </c>
-      <c r="B99" s="18" t="s">
+      <c r="B99" s="17" t="s">
         <v>1671</v>
       </c>
-      <c r="C99" s="18" t="str">
+      <c r="C99" s="17" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$125)</f>
         <v>bne 0x00100178</v>
       </c>
-      <c r="D99" s="18"/>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D99" s="17"/>
+    </row>
+    <row r="100" spans="1:4">
       <c r="A100" s="19" t="str">
         <f t="shared" si="8"/>
         <v>00100114</v>
@@ -6733,7 +6731,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4">
       <c r="A101" s="19" t="str">
         <f t="shared" si="8"/>
         <v>00100118</v>
@@ -6746,12 +6744,12 @@
       </c>
       <c r="D101" s="19"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4">
       <c r="A102" s="19" t="str">
         <f t="shared" si="8"/>
         <v>0010011C</v>
       </c>
-      <c r="B102" s="22" t="s">
+      <c r="B102" s="20" t="s">
         <v>1573</v>
       </c>
       <c r="C102" s="19" t="s">
@@ -6759,7 +6757,7 @@
       </c>
       <c r="D102" s="19"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4">
       <c r="A103" s="19" t="str">
         <f t="shared" si="8"/>
         <v>00100120</v>
@@ -6773,297 +6771,277 @@
       </c>
       <c r="D103" s="19"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" s="16" t="str">
+    <row r="104" spans="1:4">
+      <c r="A104" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100124</v>
       </c>
-      <c r="B104" s="16" t="s">
+      <c r="B104" s="3" t="s">
         <v>1646</v>
       </c>
-      <c r="C104" s="16" t="s">
+      <c r="C104" s="3" t="s">
         <v>1612</v>
       </c>
-      <c r="D104" s="16"/>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" s="16" t="str">
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100128</v>
       </c>
-      <c r="B105" s="16" t="s">
+      <c r="B105" s="3" t="s">
         <v>1647</v>
       </c>
-      <c r="C105" s="16" t="s">
+      <c r="C105" s="3" t="s">
         <v>1613</v>
       </c>
-      <c r="D105" s="16"/>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" s="16" t="str">
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="3" t="str">
         <f t="shared" si="8"/>
         <v>0010012C</v>
       </c>
-      <c r="B106" s="16" t="s">
+      <c r="B106" s="3" t="s">
         <v>1593</v>
       </c>
-      <c r="C106" s="16" t="s">
+      <c r="C106" s="3" t="s">
         <v>1587</v>
       </c>
-      <c r="D106" s="16"/>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" s="16" t="str">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100130</v>
       </c>
-      <c r="B107" s="16" t="s">
+      <c r="B107" s="3" t="s">
         <v>1648</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>1614</v>
       </c>
-      <c r="D107" s="16"/>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" s="16" t="str">
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100134</v>
       </c>
-      <c r="B108" s="16" t="s">
+      <c r="B108" s="3" t="s">
         <v>1649</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>1615</v>
       </c>
-      <c r="D108" s="16"/>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" s="16" t="str">
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100138</v>
       </c>
-      <c r="B109" s="16" t="s">
+      <c r="B109" s="3" t="s">
         <v>1650</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>1616</v>
       </c>
-      <c r="D109" s="16"/>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" s="16" t="str">
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="3" t="str">
         <f t="shared" si="8"/>
         <v>0010013C</v>
       </c>
-      <c r="B110" s="16" t="s">
+      <c r="B110" s="3" t="s">
         <v>1592</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>1585</v>
       </c>
-      <c r="D110" s="16"/>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" s="16" t="str">
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100140</v>
       </c>
-      <c r="B111" s="16" t="s">
+      <c r="B111" s="3" t="s">
         <v>1673</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>1664</v>
       </c>
-      <c r="D111" s="16" t="s">
+      <c r="D111" s="3" t="s">
         <v>1665</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" s="16" t="str">
+    <row r="112" spans="1:4">
+      <c r="A112" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100144</v>
       </c>
-      <c r="B112" s="16" t="s">
+      <c r="B112" s="3" t="s">
         <v>1652</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>1618</v>
       </c>
-      <c r="D112" s="16"/>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" s="16" t="str">
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100148</v>
       </c>
-      <c r="B113" s="16" t="s">
+      <c r="B113" s="3" t="s">
         <v>1653</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>1623</v>
       </c>
-      <c r="D113" s="16"/>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A114" s="16" t="str">
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="3" t="str">
         <f t="shared" si="8"/>
         <v>0010014C</v>
       </c>
-      <c r="B114" s="16" t="s">
+      <c r="B114" s="3" t="s">
         <v>1674</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>1666</v>
       </c>
-      <c r="D114" s="16">
+      <c r="D114" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A115" s="16" t="str">
+    <row r="115" spans="1:4">
+      <c r="A115" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100150</v>
       </c>
-      <c r="B115" s="16" t="s">
+      <c r="B115" s="3" t="s">
         <v>1654</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>1625</v>
       </c>
-      <c r="D115" s="16"/>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A116" s="16" t="str">
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100154</v>
       </c>
-      <c r="B116" s="16" t="s">
+      <c r="B116" s="3" t="s">
         <v>1655</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>1619</v>
       </c>
-      <c r="D116" s="16"/>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A117" s="16" t="str">
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100158</v>
       </c>
-      <c r="B117" s="17" t="s">
+      <c r="B117" s="4" t="s">
         <v>1656</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>1624</v>
       </c>
-      <c r="D117" s="16"/>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A118" s="16" t="str">
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="3" t="str">
         <f t="shared" si="8"/>
         <v>0010015C</v>
       </c>
-      <c r="B118" s="16" t="s">
+      <c r="B118" s="3" t="s">
         <v>1657</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>1620</v>
       </c>
-      <c r="D118" s="16"/>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A119" s="16" t="str">
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100160</v>
       </c>
-      <c r="B119" s="16" t="s">
+      <c r="B119" s="3" t="s">
         <v>1651</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>1617</v>
       </c>
-      <c r="D119" s="16"/>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120" s="16" t="str">
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100164</v>
       </c>
-      <c r="B120" s="16" t="s">
+      <c r="B120" s="3" t="s">
         <v>1658</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>1621</v>
       </c>
-      <c r="D120" s="16"/>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121" s="16" t="str">
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100168</v>
       </c>
-      <c r="B121" s="16" t="s">
+      <c r="B121" s="3" t="s">
         <v>1593</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>1587</v>
       </c>
-      <c r="D121" s="16"/>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122" s="16" t="str">
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="3" t="str">
         <f t="shared" si="8"/>
         <v>0010016C</v>
       </c>
-      <c r="B122" s="16" t="s">
+      <c r="B122" s="3" t="s">
         <v>1659</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>1622</v>
       </c>
-      <c r="D122" s="16"/>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A123" s="16" t="str">
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100170</v>
       </c>
-      <c r="B123" s="16" t="s">
+      <c r="B123" s="3" t="s">
         <v>1660</v>
       </c>
-      <c r="C123" s="16" t="str">
+      <c r="C123" s="3" t="str">
         <f>SUBSTITUTE(C74,"push","pop")</f>
         <v>pop {r4, r5, r6, lr}</v>
       </c>
-      <c r="D123" s="16"/>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A124" s="16" t="str">
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100174</v>
       </c>
-      <c r="B124" s="16" t="s">
+      <c r="B124" s="3" t="s">
         <v>1675</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>1626</v>
       </c>
-      <c r="D124" s="16"/>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" s="16" t="str">
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="3" t="str">
         <f t="shared" si="8"/>
         <v>00100178</v>
       </c>
-      <c r="B125" s="16" t="s">
+      <c r="B125" s="3" t="s">
         <v>1574</v>
       </c>
-      <c r="C125" s="16" t="str">
+      <c r="C125" s="3" t="str">
         <f>SUBSTITUTE(C123,"lr","pc")</f>
         <v>pop {r4, r5, r6, pc}</v>
       </c>
-      <c r="D125" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7074,9 +7052,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139B9424-3B4D-4D48-9D45-E0A0451C9CA6}">
   <dimension ref="A1:R808"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.15"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -7091,7 +7069,7 @@
         <v>08</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -7110,7 +7088,7 @@
       </c>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -7129,7 +7107,7 @@
       </c>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -7148,7 +7126,7 @@
       </c>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -7167,7 +7145,7 @@
       </c>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -7186,7 +7164,7 @@
       </c>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:18">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -7205,7 +7183,7 @@
       </c>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -7224,7 +7202,7 @@
       </c>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:18">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -7243,7 +7221,7 @@
       </c>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:18">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -7262,7 +7240,7 @@
       </c>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:18">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -7281,7 +7259,7 @@
       </c>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:18">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -7300,7 +7278,7 @@
       </c>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:18">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -7319,7 +7297,7 @@
       </c>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:18">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -7338,7 +7316,7 @@
       </c>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:18">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -7356,7 +7334,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:18">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -7375,7 +7353,7 @@
       </c>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:18">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -7394,7 +7372,7 @@
       </c>
       <c r="R17" s="1"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:18">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -7417,7 +7395,7 @@
       </c>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:18">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -7425,7 +7403,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:18">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -7434,7 +7412,7 @@
       </c>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:18">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -7443,7 +7421,7 @@
       </c>
       <c r="R21" s="1"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:18">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -7452,7 +7430,7 @@
       </c>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:18">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -7461,7 +7439,7 @@
       </c>
       <c r="R23" s="1"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:18">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -7470,7 +7448,7 @@
       </c>
       <c r="R24" s="1"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:18">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -7479,7 +7457,7 @@
       </c>
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:18">
       <c r="A26" t="s">
         <v>46</v>
       </c>
@@ -7488,7 +7466,7 @@
       </c>
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:18">
       <c r="A27" t="s">
         <v>47</v>
       </c>
@@ -7497,7 +7475,7 @@
       </c>
       <c r="R27" s="1"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:18">
       <c r="A28" t="s">
         <v>48</v>
       </c>
@@ -7506,7 +7484,7 @@
       </c>
       <c r="R28" s="1"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:18">
       <c r="A29" t="s">
         <v>49</v>
       </c>
@@ -7515,7 +7493,7 @@
       </c>
       <c r="R29" s="1"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:18">
       <c r="A30" t="s">
         <v>50</v>
       </c>
@@ -7524,7 +7502,7 @@
       </c>
       <c r="R30" s="1"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:18">
       <c r="A31" t="s">
         <v>51</v>
       </c>
@@ -7533,7 +7511,7 @@
       </c>
       <c r="R31" s="1"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:18">
       <c r="A32" t="s">
         <v>52</v>
       </c>
@@ -7542,7 +7520,7 @@
       </c>
       <c r="R32" s="1"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:18">
       <c r="A33" t="s">
         <v>53</v>
       </c>
@@ -7551,7 +7529,7 @@
       </c>
       <c r="R33" s="1"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:18">
       <c r="A34" t="s">
         <v>54</v>
       </c>
@@ -7560,7 +7538,7 @@
       </c>
       <c r="R34" s="1"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:18">
       <c r="A35" t="s">
         <v>55</v>
       </c>
@@ -7569,7 +7547,7 @@
       </c>
       <c r="R35" s="1"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:18">
       <c r="A36" t="s">
         <v>56</v>
       </c>
@@ -7578,7 +7556,7 @@
       </c>
       <c r="R36" s="1"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:18">
       <c r="A37" t="s">
         <v>57</v>
       </c>
@@ -7587,7 +7565,7 @@
       </c>
       <c r="R37" s="1"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:18">
       <c r="A38" t="s">
         <v>58</v>
       </c>
@@ -7596,7 +7574,7 @@
       </c>
       <c r="R38" s="1"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:18">
       <c r="A39" t="s">
         <v>59</v>
       </c>
@@ -7605,7 +7583,7 @@
       </c>
       <c r="R39" s="1"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:18">
       <c r="A40" t="s">
         <v>60</v>
       </c>
@@ -7614,7 +7592,7 @@
       </c>
       <c r="R40" s="1"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:18">
       <c r="A41" t="s">
         <v>61</v>
       </c>
@@ -7623,7 +7601,7 @@
       </c>
       <c r="R41" s="1"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:18">
       <c r="A42" t="s">
         <v>62</v>
       </c>
@@ -7632,7 +7610,7 @@
       </c>
       <c r="R42" s="1"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:18">
       <c r="A43" t="s">
         <v>63</v>
       </c>
@@ -7641,7 +7619,7 @@
       </c>
       <c r="R43" s="1"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:18">
       <c r="A44" t="s">
         <v>64</v>
       </c>
@@ -7650,7 +7628,7 @@
       </c>
       <c r="R44" s="1"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:18">
       <c r="A45" t="s">
         <v>65</v>
       </c>
@@ -7659,7 +7637,7 @@
       </c>
       <c r="R45" s="1"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:18">
       <c r="A46" t="s">
         <v>66</v>
       </c>
@@ -7668,7 +7646,7 @@
       </c>
       <c r="R46" s="1"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:18">
       <c r="A47" t="s">
         <v>67</v>
       </c>
@@ -7676,7 +7654,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:18">
       <c r="A48" t="s">
         <v>68</v>
       </c>
@@ -7685,7 +7663,7 @@
       </c>
       <c r="R48" s="1"/>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:18">
       <c r="A49" t="s">
         <v>69</v>
       </c>
@@ -7694,7 +7672,7 @@
       </c>
       <c r="R49" s="1"/>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:18">
       <c r="A50" t="s">
         <v>70</v>
       </c>
@@ -7703,7 +7681,7 @@
       </c>
       <c r="R50" s="1"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:18">
       <c r="A51" t="s">
         <v>71</v>
       </c>
@@ -7712,7 +7690,7 @@
       </c>
       <c r="R51" s="1"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:18">
       <c r="A52" t="s">
         <v>72</v>
       </c>
@@ -7721,7 +7699,7 @@
       </c>
       <c r="R52" s="1"/>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:18">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -7730,7 +7708,7 @@
       </c>
       <c r="R53" s="1"/>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:18">
       <c r="A54" t="s">
         <v>74</v>
       </c>
@@ -7739,7 +7717,7 @@
       </c>
       <c r="R54" s="1"/>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:18">
       <c r="A55" t="s">
         <v>75</v>
       </c>
@@ -7747,7 +7725,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:18">
       <c r="A56" t="s">
         <v>76</v>
       </c>
@@ -7756,7 +7734,7 @@
       </c>
       <c r="R56" s="1"/>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:18">
       <c r="A57" t="s">
         <v>77</v>
       </c>
@@ -7765,7 +7743,7 @@
       </c>
       <c r="R57" s="1"/>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:18">
       <c r="A58" t="s">
         <v>78</v>
       </c>
@@ -7774,7 +7752,7 @@
       </c>
       <c r="R58" s="1"/>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:18">
       <c r="A59" t="s">
         <v>79</v>
       </c>
@@ -7783,7 +7761,7 @@
       </c>
       <c r="R59" s="1"/>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:18">
       <c r="A60" t="s">
         <v>80</v>
       </c>
@@ -7792,7 +7770,7 @@
       </c>
       <c r="R60" s="1"/>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:18">
       <c r="A61" t="s">
         <v>81</v>
       </c>
@@ -7801,7 +7779,7 @@
       </c>
       <c r="R61" s="1"/>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:18">
       <c r="A62" t="s">
         <v>82</v>
       </c>
@@ -7810,7 +7788,7 @@
       </c>
       <c r="R62" s="1"/>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:18">
       <c r="A63" t="s">
         <v>83</v>
       </c>
@@ -7819,7 +7797,7 @@
       </c>
       <c r="R63" s="1"/>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:18">
       <c r="A64" t="s">
         <v>84</v>
       </c>
@@ -7828,7 +7806,7 @@
       </c>
       <c r="R64" s="1"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:18">
       <c r="A65" t="s">
         <v>85</v>
       </c>
@@ -7837,7 +7815,7 @@
       </c>
       <c r="R65" s="1"/>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:18">
       <c r="A66" t="s">
         <v>86</v>
       </c>
@@ -7846,7 +7824,7 @@
       </c>
       <c r="R66" s="1"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:18">
       <c r="A67" t="s">
         <v>87</v>
       </c>
@@ -7855,7 +7833,7 @@
       </c>
       <c r="R67" s="1"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:18">
       <c r="A68" t="s">
         <v>88</v>
       </c>
@@ -7864,7 +7842,7 @@
       </c>
       <c r="R68" s="1"/>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:18">
       <c r="A69" t="s">
         <v>89</v>
       </c>
@@ -7873,7 +7851,7 @@
       </c>
       <c r="R69" s="1"/>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:18">
       <c r="A70" t="s">
         <v>90</v>
       </c>
@@ -7882,7 +7860,7 @@
       </c>
       <c r="R70" s="1"/>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:18">
       <c r="A71" t="s">
         <v>91</v>
       </c>
@@ -7891,7 +7869,7 @@
       </c>
       <c r="R71" s="1"/>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:18">
       <c r="A72" t="s">
         <v>92</v>
       </c>
@@ -7900,7 +7878,7 @@
       </c>
       <c r="R72" s="1"/>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:18">
       <c r="A73" t="s">
         <v>93</v>
       </c>
@@ -7909,7 +7887,7 @@
       </c>
       <c r="R73" s="1"/>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:18">
       <c r="A74" t="s">
         <v>94</v>
       </c>
@@ -7918,7 +7896,7 @@
       </c>
       <c r="R74" s="1"/>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:18">
       <c r="A75" t="s">
         <v>95</v>
       </c>
@@ -7926,7 +7904,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:18">
       <c r="A76" t="s">
         <v>96</v>
       </c>
@@ -7935,7 +7913,7 @@
       </c>
       <c r="R76" s="1"/>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:18">
       <c r="A77" t="s">
         <v>97</v>
       </c>
@@ -7944,7 +7922,7 @@
       </c>
       <c r="R77" s="1"/>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:18">
       <c r="A78" t="s">
         <v>98</v>
       </c>
@@ -7953,7 +7931,7 @@
       </c>
       <c r="R78" s="1"/>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:18">
       <c r="A79" t="s">
         <v>99</v>
       </c>
@@ -7962,7 +7940,7 @@
       </c>
       <c r="R79" s="1"/>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:18">
       <c r="A80" t="s">
         <v>100</v>
       </c>
@@ -7971,7 +7949,7 @@
       </c>
       <c r="R80" s="1"/>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:18">
       <c r="A81" t="s">
         <v>101</v>
       </c>
@@ -7980,7 +7958,7 @@
       </c>
       <c r="R81" s="1"/>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:18">
       <c r="A82" t="s">
         <v>102</v>
       </c>
@@ -7989,7 +7967,7 @@
       </c>
       <c r="R82" s="1"/>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:18">
       <c r="A83" t="s">
         <v>103</v>
       </c>
@@ -7998,7 +7976,7 @@
       </c>
       <c r="R83" s="1"/>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:18">
       <c r="A84" t="s">
         <v>104</v>
       </c>
@@ -8007,7 +7985,7 @@
       </c>
       <c r="R84" s="1"/>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:18">
       <c r="A85" t="s">
         <v>105</v>
       </c>
@@ -8016,7 +7994,7 @@
       </c>
       <c r="R85" s="1"/>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:18">
       <c r="A86" t="s">
         <v>106</v>
       </c>
@@ -8025,7 +8003,7 @@
       </c>
       <c r="R86" s="1"/>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:18">
       <c r="A87" t="s">
         <v>107</v>
       </c>
@@ -8034,7 +8012,7 @@
       </c>
       <c r="R87" s="1"/>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:18">
       <c r="A88" t="s">
         <v>108</v>
       </c>
@@ -8043,7 +8021,7 @@
       </c>
       <c r="R88" s="1"/>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:18">
       <c r="A89" t="s">
         <v>109</v>
       </c>
@@ -8052,7 +8030,7 @@
       </c>
       <c r="R89" s="1"/>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:18">
       <c r="A90" t="s">
         <v>110</v>
       </c>
@@ -8061,7 +8039,7 @@
       </c>
       <c r="R90" s="1"/>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:18">
       <c r="A91" t="s">
         <v>111</v>
       </c>
@@ -8070,7 +8048,7 @@
       </c>
       <c r="R91" s="1"/>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:18">
       <c r="A92" t="s">
         <v>112</v>
       </c>
@@ -8079,7 +8057,7 @@
       </c>
       <c r="R92" s="1"/>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:18">
       <c r="A93" t="s">
         <v>113</v>
       </c>
@@ -8088,7 +8066,7 @@
       </c>
       <c r="R93" s="1"/>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:18">
       <c r="A94" t="s">
         <v>114</v>
       </c>
@@ -8097,7 +8075,7 @@
       </c>
       <c r="R94" s="1"/>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:18">
       <c r="A95" t="s">
         <v>115</v>
       </c>
@@ -8106,7 +8084,7 @@
       </c>
       <c r="R95" s="1"/>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:18">
       <c r="A96" t="s">
         <v>116</v>
       </c>
@@ -8115,7 +8093,7 @@
       </c>
       <c r="R96" s="1"/>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:18">
       <c r="A97" t="s">
         <v>117</v>
       </c>
@@ -8123,7 +8101,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:18">
       <c r="A98" t="s">
         <v>118</v>
       </c>
@@ -8131,7 +8109,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:18">
       <c r="A99" t="s">
         <v>119</v>
       </c>
@@ -8140,7 +8118,7 @@
       </c>
       <c r="R99" s="1"/>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:18">
       <c r="A100" t="s">
         <v>120</v>
       </c>
@@ -8149,7 +8127,7 @@
       </c>
       <c r="R100" s="1"/>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:18">
       <c r="A101" t="s">
         <v>121</v>
       </c>
@@ -8157,7 +8135,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:18">
       <c r="A102" t="s">
         <v>122</v>
       </c>
@@ -8166,7 +8144,7 @@
       </c>
       <c r="R102" s="1"/>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:18">
       <c r="A103" t="s">
         <v>123</v>
       </c>
@@ -8174,7 +8152,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:18">
       <c r="A104" t="s">
         <v>124</v>
       </c>
@@ -8183,7 +8161,7 @@
       </c>
       <c r="R104" s="1"/>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:18">
       <c r="A105" t="s">
         <v>125</v>
       </c>
@@ -8191,7 +8169,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:18">
       <c r="A106" t="s">
         <v>126</v>
       </c>
@@ -8199,7 +8177,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:18">
       <c r="A107" t="s">
         <v>127</v>
       </c>
@@ -8207,7 +8185,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:18">
       <c r="A108" t="s">
         <v>128</v>
       </c>
@@ -8215,7 +8193,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:18">
       <c r="A109" t="s">
         <v>129</v>
       </c>
@@ -8224,7 +8202,7 @@
       </c>
       <c r="R109" s="1"/>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:18">
       <c r="A110" t="s">
         <v>130</v>
       </c>
@@ -8233,7 +8211,7 @@
       </c>
       <c r="R110" s="1"/>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:18">
       <c r="A111" t="s">
         <v>131</v>
       </c>
@@ -8241,7 +8219,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:18">
       <c r="A112" t="s">
         <v>132</v>
       </c>
@@ -8249,7 +8227,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:18">
       <c r="A113" t="s">
         <v>133</v>
       </c>
@@ -8257,7 +8235,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:18">
       <c r="A114" t="s">
         <v>134</v>
       </c>
@@ -8265,7 +8243,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:18">
       <c r="A115" t="s">
         <v>135</v>
       </c>
@@ -8273,7 +8251,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:18">
       <c r="A116" t="s">
         <v>136</v>
       </c>
@@ -8281,7 +8259,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:18">
       <c r="A117" t="s">
         <v>137</v>
       </c>
@@ -8289,7 +8267,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:18">
       <c r="A118" t="s">
         <v>138</v>
       </c>
@@ -8297,7 +8275,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:18">
       <c r="A119" t="s">
         <v>139</v>
       </c>
@@ -8305,7 +8283,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:18">
       <c r="A120" t="s">
         <v>140</v>
       </c>
@@ -8313,7 +8291,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:18">
       <c r="A121" t="s">
         <v>141</v>
       </c>
@@ -8322,7 +8300,7 @@
       </c>
       <c r="R121" s="1"/>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:18">
       <c r="A122" t="s">
         <v>142</v>
       </c>
@@ -8331,7 +8309,7 @@
       </c>
       <c r="R122" s="1"/>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:18">
       <c r="A123" t="s">
         <v>143</v>
       </c>
@@ -8340,7 +8318,7 @@
       </c>
       <c r="R123" s="1"/>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:18">
       <c r="A124" t="s">
         <v>144</v>
       </c>
@@ -8349,7 +8327,7 @@
       </c>
       <c r="R124" s="1"/>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:18">
       <c r="A125" t="s">
         <v>145</v>
       </c>
@@ -8358,7 +8336,7 @@
       </c>
       <c r="R125" s="1"/>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:18">
       <c r="A126" t="s">
         <v>146</v>
       </c>
@@ -8367,7 +8345,7 @@
       </c>
       <c r="R126" s="1"/>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:18">
       <c r="A127" t="s">
         <v>147</v>
       </c>
@@ -8376,7 +8354,7 @@
       </c>
       <c r="R127" s="1"/>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:18">
       <c r="A128" t="s">
         <v>148</v>
       </c>
@@ -8385,7 +8363,7 @@
       </c>
       <c r="R128" s="1"/>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:18">
       <c r="A129" t="s">
         <v>149</v>
       </c>
@@ -8394,7 +8372,7 @@
       </c>
       <c r="R129" s="1"/>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:18">
       <c r="A130" t="s">
         <v>150</v>
       </c>
@@ -8402,7 +8380,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:18">
       <c r="A131" t="s">
         <v>151</v>
       </c>
@@ -8411,7 +8389,7 @@
       </c>
       <c r="R131" s="1"/>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:18">
       <c r="A132" t="s">
         <v>152</v>
       </c>
@@ -8420,7 +8398,7 @@
       </c>
       <c r="R132" s="1"/>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:18">
       <c r="A133" t="s">
         <v>153</v>
       </c>
@@ -8429,7 +8407,7 @@
       </c>
       <c r="R133" s="1"/>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:18">
       <c r="A134" t="s">
         <v>154</v>
       </c>
@@ -8437,7 +8415,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:18">
       <c r="A135" t="s">
         <v>155</v>
       </c>
@@ -8446,7 +8424,7 @@
       </c>
       <c r="R135" s="1"/>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:18">
       <c r="A136" t="s">
         <v>156</v>
       </c>
@@ -8454,7 +8432,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:18">
       <c r="A137" t="s">
         <v>157</v>
       </c>
@@ -8463,7 +8441,7 @@
       </c>
       <c r="R137" s="1"/>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:18">
       <c r="A138" t="s">
         <v>158</v>
       </c>
@@ -8472,7 +8450,7 @@
       </c>
       <c r="R138" s="1"/>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:18">
       <c r="A139" t="s">
         <v>159</v>
       </c>
@@ -8481,7 +8459,7 @@
       </c>
       <c r="R139" s="1"/>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:18">
       <c r="A140" t="s">
         <v>160</v>
       </c>
@@ -8490,7 +8468,7 @@
       </c>
       <c r="R140" s="1"/>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:18">
       <c r="A141" t="s">
         <v>161</v>
       </c>
@@ -8499,7 +8477,7 @@
       </c>
       <c r="R141" s="1"/>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:18">
       <c r="A142" t="s">
         <v>162</v>
       </c>
@@ -8508,7 +8486,7 @@
       </c>
       <c r="R142" s="1"/>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:18">
       <c r="A143" t="s">
         <v>163</v>
       </c>
@@ -8517,7 +8495,7 @@
       </c>
       <c r="R143" s="1"/>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:18">
       <c r="A144" t="s">
         <v>164</v>
       </c>
@@ -8526,7 +8504,7 @@
       </c>
       <c r="R144" s="1"/>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:18">
       <c r="A145" t="s">
         <v>165</v>
       </c>
@@ -8534,7 +8512,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:18">
       <c r="A146" t="s">
         <v>166</v>
       </c>
@@ -8543,7 +8521,7 @@
       </c>
       <c r="R146" s="1"/>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:18">
       <c r="A147" t="s">
         <v>167</v>
       </c>
@@ -8552,7 +8530,7 @@
       </c>
       <c r="R147" s="1"/>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:18">
       <c r="A148" t="s">
         <v>168</v>
       </c>
@@ -8561,7 +8539,7 @@
       </c>
       <c r="R148" s="1"/>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:18">
       <c r="A149" t="s">
         <v>169</v>
       </c>
@@ -8570,7 +8548,7 @@
       </c>
       <c r="R149" s="1"/>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:18">
       <c r="A150" t="s">
         <v>170</v>
       </c>
@@ -8579,7 +8557,7 @@
       </c>
       <c r="R150" s="1"/>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:18">
       <c r="A151" t="s">
         <v>171</v>
       </c>
@@ -8587,7 +8565,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:18">
       <c r="A152" t="s">
         <v>172</v>
       </c>
@@ -8595,7 +8573,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:18">
       <c r="A153" t="s">
         <v>173</v>
       </c>
@@ -8604,7 +8582,7 @@
       </c>
       <c r="R153" s="1"/>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:18">
       <c r="A154" t="s">
         <v>174</v>
       </c>
@@ -8613,7 +8591,7 @@
       </c>
       <c r="R154" s="1"/>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:18">
       <c r="A155" t="s">
         <v>175</v>
       </c>
@@ -8622,7 +8600,7 @@
       </c>
       <c r="R155" s="1"/>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:18">
       <c r="A156" t="s">
         <v>176</v>
       </c>
@@ -8631,7 +8609,7 @@
       </c>
       <c r="R156" s="1"/>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:18">
       <c r="A157" t="s">
         <v>177</v>
       </c>
@@ -8639,7 +8617,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:18">
       <c r="A158" t="s">
         <v>178</v>
       </c>
@@ -8648,7 +8626,7 @@
       </c>
       <c r="R158" s="1"/>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:18">
       <c r="A159" t="s">
         <v>179</v>
       </c>
@@ -8657,7 +8635,7 @@
       </c>
       <c r="R159" s="1"/>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:18">
       <c r="A160" t="s">
         <v>180</v>
       </c>
@@ -8665,7 +8643,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:18">
       <c r="A161" t="s">
         <v>181</v>
       </c>
@@ -8673,7 +8651,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:18">
       <c r="A162" t="s">
         <v>182</v>
       </c>
@@ -8682,7 +8660,7 @@
       </c>
       <c r="R162" s="1"/>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:18">
       <c r="A163" t="s">
         <v>183</v>
       </c>
@@ -8691,7 +8669,7 @@
       </c>
       <c r="R163" s="1"/>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:18">
       <c r="A164" t="s">
         <v>184</v>
       </c>
@@ -8700,7 +8678,7 @@
       </c>
       <c r="R164" s="1"/>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:18">
       <c r="A165" t="s">
         <v>185</v>
       </c>
@@ -8708,7 +8686,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:18">
       <c r="A166" t="s">
         <v>186</v>
       </c>
@@ -8716,7 +8694,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:18">
       <c r="A167" t="s">
         <v>187</v>
       </c>
@@ -8724,7 +8702,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:18">
       <c r="A168" t="s">
         <v>188</v>
       </c>
@@ -8733,7 +8711,7 @@
       </c>
       <c r="R168" s="1"/>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:18">
       <c r="A169" t="s">
         <v>189</v>
       </c>
@@ -8742,7 +8720,7 @@
       </c>
       <c r="R169" s="1"/>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:18">
       <c r="A170" t="s">
         <v>190</v>
       </c>
@@ -8750,7 +8728,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:18">
       <c r="A171" t="s">
         <v>191</v>
       </c>
@@ -8758,7 +8736,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:18">
       <c r="A172" t="s">
         <v>192</v>
       </c>
@@ -8767,7 +8745,7 @@
       </c>
       <c r="R172" s="1"/>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:18">
       <c r="A173" t="s">
         <v>193</v>
       </c>
@@ -8776,7 +8754,7 @@
       </c>
       <c r="R173" s="1"/>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:18">
       <c r="A174" t="s">
         <v>194</v>
       </c>
@@ -8785,7 +8763,7 @@
       </c>
       <c r="R174" s="1"/>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:18">
       <c r="A175" t="s">
         <v>195</v>
       </c>
@@ -8793,7 +8771,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:18">
       <c r="A176" t="s">
         <v>196</v>
       </c>
@@ -8802,7 +8780,7 @@
       </c>
       <c r="R176" s="1"/>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:18">
       <c r="A177" t="s">
         <v>197</v>
       </c>
@@ -8810,7 +8788,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:18">
       <c r="A178" t="s">
         <v>198</v>
       </c>
@@ -8819,7 +8797,7 @@
       </c>
       <c r="R178" s="1"/>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:18">
       <c r="A179" t="s">
         <v>199</v>
       </c>
@@ -8828,7 +8806,7 @@
       </c>
       <c r="R179" s="1"/>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:18">
       <c r="A180" t="s">
         <v>200</v>
       </c>
@@ -8837,7 +8815,7 @@
       </c>
       <c r="R180" s="1"/>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:18">
       <c r="A181" t="s">
         <v>201</v>
       </c>
@@ -8846,7 +8824,7 @@
       </c>
       <c r="R181" s="1"/>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:18">
       <c r="A182" t="s">
         <v>202</v>
       </c>
@@ -8855,7 +8833,7 @@
       </c>
       <c r="R182" s="1"/>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:18">
       <c r="A183" t="s">
         <v>203</v>
       </c>
@@ -8863,7 +8841,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:18">
       <c r="A184" t="s">
         <v>204</v>
       </c>
@@ -8872,7 +8850,7 @@
       </c>
       <c r="R184" s="1"/>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:18">
       <c r="A185" t="s">
         <v>205</v>
       </c>
@@ -8881,7 +8859,7 @@
       </c>
       <c r="R185" s="1"/>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:18">
       <c r="A186" t="s">
         <v>206</v>
       </c>
@@ -8889,7 +8867,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:18">
       <c r="A187" t="s">
         <v>207</v>
       </c>
@@ -8898,7 +8876,7 @@
       </c>
       <c r="R187" s="1"/>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:18">
       <c r="A188" t="s">
         <v>208</v>
       </c>
@@ -8906,7 +8884,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:18">
       <c r="A189" t="s">
         <v>209</v>
       </c>
@@ -8915,7 +8893,7 @@
       </c>
       <c r="R189" s="1"/>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:18">
       <c r="A190" t="s">
         <v>210</v>
       </c>
@@ -8924,7 +8902,7 @@
       </c>
       <c r="R190" s="1"/>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:18">
       <c r="A191" t="s">
         <v>211</v>
       </c>
@@ -8933,7 +8911,7 @@
       </c>
       <c r="R191" s="1"/>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:18">
       <c r="A192" t="s">
         <v>212</v>
       </c>
@@ -8941,7 +8919,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:18">
       <c r="A193" t="s">
         <v>213</v>
       </c>
@@ -8950,7 +8928,7 @@
       </c>
       <c r="R193" s="1"/>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:18">
       <c r="A194" t="s">
         <v>214</v>
       </c>
@@ -8958,7 +8936,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:18">
       <c r="A195" t="s">
         <v>215</v>
       </c>
@@ -8966,7 +8944,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:18">
       <c r="A196" t="s">
         <v>216</v>
       </c>
@@ -8974,7 +8952,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:18">
       <c r="A197" t="s">
         <v>217</v>
       </c>
@@ -8983,7 +8961,7 @@
       </c>
       <c r="R197" s="1"/>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:18">
       <c r="A198" t="s">
         <v>218</v>
       </c>
@@ -8991,7 +8969,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:18">
       <c r="A199" t="s">
         <v>219</v>
       </c>
@@ -9000,7 +8978,7 @@
       </c>
       <c r="R199" s="1"/>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:18">
       <c r="A200" t="s">
         <v>220</v>
       </c>
@@ -9008,7 +8986,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:18">
       <c r="A201" t="s">
         <v>221</v>
       </c>
@@ -9017,7 +8995,7 @@
       </c>
       <c r="R201" s="1"/>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:18">
       <c r="A202" t="s">
         <v>222</v>
       </c>
@@ -9025,7 +9003,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:18">
       <c r="A203" t="s">
         <v>223</v>
       </c>
@@ -9034,7 +9012,7 @@
       </c>
       <c r="R203" s="1"/>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:18">
       <c r="A204" t="s">
         <v>224</v>
       </c>
@@ -9042,7 +9020,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:18">
       <c r="A205" t="s">
         <v>225</v>
       </c>
@@ -9051,7 +9029,7 @@
       </c>
       <c r="R205" s="1"/>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:18">
       <c r="A206" t="s">
         <v>226</v>
       </c>
@@ -9060,7 +9038,7 @@
       </c>
       <c r="R206" s="1"/>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:18">
       <c r="A207" t="s">
         <v>227</v>
       </c>
@@ -9069,7 +9047,7 @@
       </c>
       <c r="R207" s="1"/>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:18">
       <c r="A208" t="s">
         <v>228</v>
       </c>
@@ -9078,7 +9056,7 @@
       </c>
       <c r="R208" s="1"/>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:18">
       <c r="A209" t="s">
         <v>229</v>
       </c>
@@ -9086,7 +9064,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:18">
       <c r="A210" t="s">
         <v>230</v>
       </c>
@@ -9095,7 +9073,7 @@
       </c>
       <c r="R210" s="1"/>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:18">
       <c r="A211" t="s">
         <v>231</v>
       </c>
@@ -9104,7 +9082,7 @@
       </c>
       <c r="R211" s="1"/>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:18">
       <c r="A212" t="s">
         <v>232</v>
       </c>
@@ -9113,7 +9091,7 @@
       </c>
       <c r="R212" s="1"/>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:18">
       <c r="A213" t="s">
         <v>233</v>
       </c>
@@ -9121,7 +9099,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:18">
       <c r="A214" t="s">
         <v>234</v>
       </c>
@@ -9130,7 +9108,7 @@
       </c>
       <c r="R214" s="1"/>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:18">
       <c r="A215" t="s">
         <v>235</v>
       </c>
@@ -9138,7 +9116,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:18">
       <c r="A216" t="s">
         <v>236</v>
       </c>
@@ -9146,7 +9124,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:18">
       <c r="A217" t="s">
         <v>237</v>
       </c>
@@ -9155,7 +9133,7 @@
       </c>
       <c r="R217" s="1"/>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:18">
       <c r="A218" t="s">
         <v>238</v>
       </c>
@@ -9164,7 +9142,7 @@
       </c>
       <c r="R218" s="1"/>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:18">
       <c r="A219" t="s">
         <v>239</v>
       </c>
@@ -9173,7 +9151,7 @@
       </c>
       <c r="R219" s="1"/>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:18">
       <c r="A220" t="s">
         <v>240</v>
       </c>
@@ -9181,7 +9159,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:18">
       <c r="A221" t="s">
         <v>241</v>
       </c>
@@ -9189,7 +9167,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:18">
       <c r="A222" t="s">
         <v>242</v>
       </c>
@@ -9198,7 +9176,7 @@
       </c>
       <c r="R222" s="1"/>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:18">
       <c r="A223" t="s">
         <v>243</v>
       </c>
@@ -9207,7 +9185,7 @@
       </c>
       <c r="R223" s="1"/>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:18">
       <c r="A224" t="s">
         <v>244</v>
       </c>
@@ -9216,7 +9194,7 @@
       </c>
       <c r="R224" s="1"/>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:18">
       <c r="A225" t="s">
         <v>245</v>
       </c>
@@ -9225,7 +9203,7 @@
       </c>
       <c r="R225" s="1"/>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:18">
       <c r="A226" t="s">
         <v>246</v>
       </c>
@@ -9234,7 +9212,7 @@
       </c>
       <c r="R226" s="1"/>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:18">
       <c r="A227" t="s">
         <v>247</v>
       </c>
@@ -9242,7 +9220,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:18">
       <c r="A228" t="s">
         <v>248</v>
       </c>
@@ -9251,7 +9229,7 @@
       </c>
       <c r="R228" s="1"/>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:18">
       <c r="A229" t="s">
         <v>249</v>
       </c>
@@ -9260,7 +9238,7 @@
       </c>
       <c r="R229" s="1"/>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:18">
       <c r="A230" t="s">
         <v>250</v>
       </c>
@@ -9269,7 +9247,7 @@
       </c>
       <c r="R230" s="1"/>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:18">
       <c r="A231" t="s">
         <v>251</v>
       </c>
@@ -9278,7 +9256,7 @@
       </c>
       <c r="R231" s="1"/>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:18">
       <c r="A232" t="s">
         <v>252</v>
       </c>
@@ -9287,7 +9265,7 @@
       </c>
       <c r="R232" s="1"/>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:18">
       <c r="A233" t="s">
         <v>253</v>
       </c>
@@ -9296,7 +9274,7 @@
       </c>
       <c r="R233" s="1"/>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:18">
       <c r="A234" t="s">
         <v>254</v>
       </c>
@@ -9304,7 +9282,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:18">
       <c r="A235" t="s">
         <v>255</v>
       </c>
@@ -9312,7 +9290,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:18">
       <c r="A236" t="s">
         <v>256</v>
       </c>
@@ -9320,7 +9298,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:18">
       <c r="A237" t="s">
         <v>257</v>
       </c>
@@ -9328,7 +9306,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:18">
       <c r="A238" t="s">
         <v>258</v>
       </c>
@@ -9337,7 +9315,7 @@
       </c>
       <c r="R238" s="1"/>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:18">
       <c r="A239" t="s">
         <v>259</v>
       </c>
@@ -9346,7 +9324,7 @@
       </c>
       <c r="R239" s="1"/>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:18">
       <c r="A240" t="s">
         <v>260</v>
       </c>
@@ -9355,7 +9333,7 @@
       </c>
       <c r="R240" s="1"/>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:18">
       <c r="A241" t="s">
         <v>261</v>
       </c>
@@ -9363,7 +9341,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:18">
       <c r="A242" t="s">
         <v>262</v>
       </c>
@@ -9371,7 +9349,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:18">
       <c r="A243" t="s">
         <v>263</v>
       </c>
@@ -9380,7 +9358,7 @@
       </c>
       <c r="R243" s="1"/>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:18">
       <c r="A244" t="s">
         <v>264</v>
       </c>
@@ -9389,7 +9367,7 @@
       </c>
       <c r="R244" s="1"/>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:18">
       <c r="A245" t="s">
         <v>265</v>
       </c>
@@ -9397,7 +9375,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:18">
       <c r="A246" t="s">
         <v>266</v>
       </c>
@@ -9406,7 +9384,7 @@
       </c>
       <c r="R246" s="1"/>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:18">
       <c r="A247" t="s">
         <v>267</v>
       </c>
@@ -9415,7 +9393,7 @@
       </c>
       <c r="R247" s="1"/>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:18">
       <c r="A248" t="s">
         <v>268</v>
       </c>
@@ -9424,7 +9402,7 @@
       </c>
       <c r="R248" s="1"/>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:18">
       <c r="A249" t="s">
         <v>269</v>
       </c>
@@ -9433,7 +9411,7 @@
       </c>
       <c r="R249" s="1"/>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:18">
       <c r="A250" t="s">
         <v>270</v>
       </c>
@@ -9442,7 +9420,7 @@
       </c>
       <c r="R250" s="1"/>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:18">
       <c r="A251" t="s">
         <v>271</v>
       </c>
@@ -9451,7 +9429,7 @@
       </c>
       <c r="R251" s="1"/>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:18">
       <c r="A252" t="s">
         <v>272</v>
       </c>
@@ -9460,7 +9438,7 @@
       </c>
       <c r="R252" s="1"/>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:18">
       <c r="A253" t="s">
         <v>273</v>
       </c>
@@ -9469,7 +9447,7 @@
       </c>
       <c r="R253" s="1"/>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:18">
       <c r="A254" t="s">
         <v>274</v>
       </c>
@@ -9478,7 +9456,7 @@
       </c>
       <c r="R254" s="1"/>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:18">
       <c r="A255" t="s">
         <v>275</v>
       </c>
@@ -9486,7 +9464,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:18">
       <c r="A256" t="s">
         <v>276</v>
       </c>
@@ -9495,7 +9473,7 @@
       </c>
       <c r="R256" s="1"/>
     </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:18">
       <c r="A257" t="s">
         <v>277</v>
       </c>
@@ -9503,7 +9481,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:18">
       <c r="A258" t="s">
         <v>278</v>
       </c>
@@ -9512,7 +9490,7 @@
       </c>
       <c r="R258" s="1"/>
     </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:18">
       <c r="A259" t="s">
         <v>279</v>
       </c>
@@ -9520,7 +9498,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:18">
       <c r="A260" t="s">
         <v>280</v>
       </c>
@@ -9529,7 +9507,7 @@
       </c>
       <c r="R260" s="1"/>
     </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:18">
       <c r="A261" t="s">
         <v>281</v>
       </c>
@@ -9538,7 +9516,7 @@
       </c>
       <c r="R261" s="1"/>
     </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:18">
       <c r="A262" t="s">
         <v>282</v>
       </c>
@@ -9547,7 +9525,7 @@
       </c>
       <c r="R262" s="1"/>
     </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:18">
       <c r="A263" t="s">
         <v>283</v>
       </c>
@@ -9556,7 +9534,7 @@
       </c>
       <c r="R263" s="1"/>
     </row>
-    <row r="264" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:18">
       <c r="A264" t="s">
         <v>284</v>
       </c>
@@ -9565,7 +9543,7 @@
       </c>
       <c r="R264" s="1"/>
     </row>
-    <row r="265" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:18">
       <c r="A265" t="s">
         <v>285</v>
       </c>
@@ -9574,7 +9552,7 @@
       </c>
       <c r="R265" s="1"/>
     </row>
-    <row r="266" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:18">
       <c r="A266" t="s">
         <v>286</v>
       </c>
@@ -9583,7 +9561,7 @@
       </c>
       <c r="R266" s="1"/>
     </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:18">
       <c r="A267" t="s">
         <v>287</v>
       </c>
@@ -9591,7 +9569,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:18">
       <c r="A268" t="s">
         <v>288</v>
       </c>
@@ -9599,7 +9577,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:18">
       <c r="A269" t="s">
         <v>289</v>
       </c>
@@ -9607,7 +9585,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:18">
       <c r="A270" t="s">
         <v>290</v>
       </c>
@@ -9616,7 +9594,7 @@
       </c>
       <c r="R270" s="1"/>
     </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:18">
       <c r="A271" t="s">
         <v>291</v>
       </c>
@@ -9624,7 +9602,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:18">
       <c r="A272" t="s">
         <v>292</v>
       </c>
@@ -9633,7 +9611,7 @@
       </c>
       <c r="R272" s="1"/>
     </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:18">
       <c r="A273" t="s">
         <v>293</v>
       </c>
@@ -9641,7 +9619,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:18">
       <c r="A274" t="s">
         <v>294</v>
       </c>
@@ -9649,7 +9627,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:18">
       <c r="A275" t="s">
         <v>295</v>
       </c>
@@ -9657,7 +9635,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:18">
       <c r="A276" t="s">
         <v>296</v>
       </c>
@@ -9665,7 +9643,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:18">
       <c r="A277" t="s">
         <v>297</v>
       </c>
@@ -9674,7 +9652,7 @@
       </c>
       <c r="R277" s="1"/>
     </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:18">
       <c r="A278" t="s">
         <v>298</v>
       </c>
@@ -9682,7 +9660,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:18">
       <c r="A279" t="s">
         <v>299</v>
       </c>
@@ -9690,7 +9668,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:18">
       <c r="A280" t="s">
         <v>300</v>
       </c>
@@ -9699,7 +9677,7 @@
       </c>
       <c r="R280" s="1"/>
     </row>
-    <row r="281" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:18">
       <c r="A281" t="s">
         <v>301</v>
       </c>
@@ -9708,7 +9686,7 @@
       </c>
       <c r="R281" s="1"/>
     </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:18">
       <c r="A282" t="s">
         <v>302</v>
       </c>
@@ -9716,7 +9694,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:18">
       <c r="A283" t="s">
         <v>303</v>
       </c>
@@ -9725,7 +9703,7 @@
       </c>
       <c r="R283" s="1"/>
     </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:18">
       <c r="A284" t="s">
         <v>304</v>
       </c>
@@ -9734,7 +9712,7 @@
       </c>
       <c r="R284" s="1"/>
     </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:18">
       <c r="A285" t="s">
         <v>305</v>
       </c>
@@ -9743,7 +9721,7 @@
       </c>
       <c r="R285" s="1"/>
     </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:18">
       <c r="A286" t="s">
         <v>306</v>
       </c>
@@ -9751,7 +9729,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:18">
       <c r="A287" t="s">
         <v>307</v>
       </c>
@@ -9759,7 +9737,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:18">
       <c r="A288" t="s">
         <v>308</v>
       </c>
@@ -9767,7 +9745,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="289" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:18">
       <c r="A289" t="s">
         <v>309</v>
       </c>
@@ -9775,7 +9753,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="290" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:18">
       <c r="A290" t="s">
         <v>310</v>
       </c>
@@ -9783,7 +9761,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="291" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:18">
       <c r="A291" t="s">
         <v>311</v>
       </c>
@@ -9792,7 +9770,7 @@
       </c>
       <c r="R291" s="1"/>
     </row>
-    <row r="292" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:18">
       <c r="A292" t="s">
         <v>312</v>
       </c>
@@ -9801,7 +9779,7 @@
       </c>
       <c r="R292" s="1"/>
     </row>
-    <row r="293" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:18">
       <c r="A293" t="s">
         <v>313</v>
       </c>
@@ -9810,7 +9788,7 @@
       </c>
       <c r="R293" s="1"/>
     </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:18">
       <c r="A294" t="s">
         <v>314</v>
       </c>
@@ -9818,7 +9796,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:18">
       <c r="A295" t="s">
         <v>315</v>
       </c>
@@ -9826,7 +9804,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="296" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:18">
       <c r="A296" t="s">
         <v>316</v>
       </c>
@@ -9835,7 +9813,7 @@
       </c>
       <c r="R296" s="1"/>
     </row>
-    <row r="297" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:18">
       <c r="A297" t="s">
         <v>317</v>
       </c>
@@ -9844,7 +9822,7 @@
       </c>
       <c r="R297" s="1"/>
     </row>
-    <row r="298" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:18">
       <c r="A298" t="s">
         <v>318</v>
       </c>
@@ -9853,7 +9831,7 @@
       </c>
       <c r="R298" s="1"/>
     </row>
-    <row r="299" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:18">
       <c r="A299" t="s">
         <v>319</v>
       </c>
@@ -9862,7 +9840,7 @@
       </c>
       <c r="R299" s="1"/>
     </row>
-    <row r="300" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:18">
       <c r="A300" t="s">
         <v>320</v>
       </c>
@@ -9871,7 +9849,7 @@
       </c>
       <c r="R300" s="1"/>
     </row>
-    <row r="301" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:18">
       <c r="A301" t="s">
         <v>321</v>
       </c>
@@ -9879,7 +9857,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="302" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:18">
       <c r="A302" t="s">
         <v>322</v>
       </c>
@@ -9888,7 +9866,7 @@
       </c>
       <c r="R302" s="1"/>
     </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:18">
       <c r="A303" t="s">
         <v>323</v>
       </c>
@@ -9897,7 +9875,7 @@
       </c>
       <c r="R303" s="1"/>
     </row>
-    <row r="304" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:18">
       <c r="A304" t="s">
         <v>324</v>
       </c>
@@ -9905,7 +9883,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:18">
       <c r="A305" t="s">
         <v>325</v>
       </c>
@@ -9914,7 +9892,7 @@
       </c>
       <c r="R305" s="1"/>
     </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:18">
       <c r="A306" t="s">
         <v>326</v>
       </c>
@@ -9923,7 +9901,7 @@
       </c>
       <c r="R306" s="1"/>
     </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:18">
       <c r="A307" t="s">
         <v>327</v>
       </c>
@@ -9932,7 +9910,7 @@
       </c>
       <c r="R307" s="1"/>
     </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:18">
       <c r="A308" t="s">
         <v>328</v>
       </c>
@@ -9941,7 +9919,7 @@
       </c>
       <c r="R308" s="1"/>
     </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:18">
       <c r="A309" t="s">
         <v>329</v>
       </c>
@@ -9950,7 +9928,7 @@
       </c>
       <c r="R309" s="1"/>
     </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:18">
       <c r="A310" t="s">
         <v>330</v>
       </c>
@@ -9959,7 +9937,7 @@
       </c>
       <c r="R310" s="1"/>
     </row>
-    <row r="311" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:18">
       <c r="A311" t="s">
         <v>331</v>
       </c>
@@ -9968,7 +9946,7 @@
       </c>
       <c r="R311" s="1"/>
     </row>
-    <row r="312" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:18">
       <c r="A312" t="s">
         <v>332</v>
       </c>
@@ -9977,7 +9955,7 @@
       </c>
       <c r="R312" s="1"/>
     </row>
-    <row r="313" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:18">
       <c r="A313" t="s">
         <v>333</v>
       </c>
@@ -9985,7 +9963,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="314" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:18">
       <c r="A314" t="s">
         <v>334</v>
       </c>
@@ -9994,7 +9972,7 @@
       </c>
       <c r="R314" s="1"/>
     </row>
-    <row r="315" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:18">
       <c r="A315" t="s">
         <v>335</v>
       </c>
@@ -10003,7 +9981,7 @@
       </c>
       <c r="R315" s="1"/>
     </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:18">
       <c r="A316" t="s">
         <v>336</v>
       </c>
@@ -10012,7 +9990,7 @@
       </c>
       <c r="R316" s="1"/>
     </row>
-    <row r="317" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:18">
       <c r="A317" t="s">
         <v>337</v>
       </c>
@@ -10020,7 +9998,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:18">
       <c r="A318" t="s">
         <v>338</v>
       </c>
@@ -10029,7 +10007,7 @@
       </c>
       <c r="R318" s="1"/>
     </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:18">
       <c r="A319" t="s">
         <v>339</v>
       </c>
@@ -10038,7 +10016,7 @@
       </c>
       <c r="R319" s="1"/>
     </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:18">
       <c r="A320" t="s">
         <v>340</v>
       </c>
@@ -10047,7 +10025,7 @@
       </c>
       <c r="R320" s="1"/>
     </row>
-    <row r="321" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:18">
       <c r="A321" t="s">
         <v>341</v>
       </c>
@@ -10056,7 +10034,7 @@
       </c>
       <c r="R321" s="1"/>
     </row>
-    <row r="322" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:18">
       <c r="A322" t="s">
         <v>342</v>
       </c>
@@ -10065,7 +10043,7 @@
       </c>
       <c r="R322" s="1"/>
     </row>
-    <row r="323" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:18">
       <c r="A323" t="s">
         <v>343</v>
       </c>
@@ -10073,7 +10051,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="324" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:18">
       <c r="A324" t="s">
         <v>344</v>
       </c>
@@ -10082,7 +10060,7 @@
       </c>
       <c r="R324" s="1"/>
     </row>
-    <row r="325" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:18">
       <c r="A325" t="s">
         <v>345</v>
       </c>
@@ -10091,7 +10069,7 @@
       </c>
       <c r="R325" s="1"/>
     </row>
-    <row r="326" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:18">
       <c r="A326" t="s">
         <v>346</v>
       </c>
@@ -10099,7 +10077,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="327" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:18">
       <c r="A327" t="s">
         <v>347</v>
       </c>
@@ -10108,7 +10086,7 @@
       </c>
       <c r="R327" s="1"/>
     </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:18">
       <c r="A328" t="s">
         <v>348</v>
       </c>
@@ -10117,7 +10095,7 @@
       </c>
       <c r="R328" s="1"/>
     </row>
-    <row r="329" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:18">
       <c r="A329" t="s">
         <v>349</v>
       </c>
@@ -10126,7 +10104,7 @@
       </c>
       <c r="R329" s="1"/>
     </row>
-    <row r="330" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:18">
       <c r="A330" t="s">
         <v>350</v>
       </c>
@@ -10135,7 +10113,7 @@
       </c>
       <c r="R330" s="1"/>
     </row>
-    <row r="331" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:18">
       <c r="A331" t="s">
         <v>351</v>
       </c>
@@ -10144,7 +10122,7 @@
       </c>
       <c r="R331" s="1"/>
     </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:18">
       <c r="A332" t="s">
         <v>352</v>
       </c>
@@ -10153,7 +10131,7 @@
       </c>
       <c r="R332" s="1"/>
     </row>
-    <row r="333" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:18">
       <c r="A333" t="s">
         <v>353</v>
       </c>
@@ -10161,7 +10139,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="334" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:18">
       <c r="A334" t="s">
         <v>354</v>
       </c>
@@ -10170,7 +10148,7 @@
       </c>
       <c r="R334" s="1"/>
     </row>
-    <row r="335" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:18">
       <c r="A335" t="s">
         <v>355</v>
       </c>
@@ -10178,7 +10156,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="336" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:18">
       <c r="A336" t="s">
         <v>356</v>
       </c>
@@ -10186,7 +10164,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="337" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:18">
       <c r="A337" t="s">
         <v>357</v>
       </c>
@@ -10194,7 +10172,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="338" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:18">
       <c r="A338" t="s">
         <v>358</v>
       </c>
@@ -10203,7 +10181,7 @@
       </c>
       <c r="R338" s="1"/>
     </row>
-    <row r="339" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:18">
       <c r="A339" t="s">
         <v>359</v>
       </c>
@@ -10212,7 +10190,7 @@
       </c>
       <c r="R339" s="1"/>
     </row>
-    <row r="340" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:18">
       <c r="A340" t="s">
         <v>360</v>
       </c>
@@ -10220,7 +10198,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="341" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:18">
       <c r="A341" t="s">
         <v>361</v>
       </c>
@@ -10229,7 +10207,7 @@
       </c>
       <c r="R341" s="1"/>
     </row>
-    <row r="342" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:18">
       <c r="A342" t="s">
         <v>362</v>
       </c>
@@ -10238,7 +10216,7 @@
       </c>
       <c r="R342" s="1"/>
     </row>
-    <row r="343" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:18">
       <c r="A343" t="s">
         <v>363</v>
       </c>
@@ -10247,7 +10225,7 @@
       </c>
       <c r="R343" s="1"/>
     </row>
-    <row r="344" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:18">
       <c r="A344" t="s">
         <v>364</v>
       </c>
@@ -10256,7 +10234,7 @@
       </c>
       <c r="R344" s="1"/>
     </row>
-    <row r="345" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:18">
       <c r="A345" t="s">
         <v>365</v>
       </c>
@@ -10265,7 +10243,7 @@
       </c>
       <c r="R345" s="1"/>
     </row>
-    <row r="346" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:18">
       <c r="A346" t="s">
         <v>366</v>
       </c>
@@ -10273,7 +10251,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="347" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:18">
       <c r="A347" t="s">
         <v>367</v>
       </c>
@@ -10281,7 +10259,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="348" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:18">
       <c r="A348" t="s">
         <v>368</v>
       </c>
@@ -10289,7 +10267,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="349" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:18">
       <c r="A349" t="s">
         <v>369</v>
       </c>
@@ -10298,7 +10276,7 @@
       </c>
       <c r="R349" s="1"/>
     </row>
-    <row r="350" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:18">
       <c r="A350" t="s">
         <v>370</v>
       </c>
@@ -10306,7 +10284,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="351" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:18">
       <c r="A351" t="s">
         <v>371</v>
       </c>
@@ -10315,7 +10293,7 @@
       </c>
       <c r="R351" s="1"/>
     </row>
-    <row r="352" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:18">
       <c r="A352" t="s">
         <v>372</v>
       </c>
@@ -10323,7 +10301,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="353" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:18">
       <c r="A353" t="s">
         <v>373</v>
       </c>
@@ -10332,7 +10310,7 @@
       </c>
       <c r="R353" s="1"/>
     </row>
-    <row r="354" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:18">
       <c r="A354" t="s">
         <v>374</v>
       </c>
@@ -10341,7 +10319,7 @@
       </c>
       <c r="R354" s="1"/>
     </row>
-    <row r="355" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:18">
       <c r="A355" t="s">
         <v>375</v>
       </c>
@@ -10350,7 +10328,7 @@
       </c>
       <c r="R355" s="1"/>
     </row>
-    <row r="356" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:18">
       <c r="A356" t="s">
         <v>376</v>
       </c>
@@ -10358,7 +10336,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="357" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:18">
       <c r="A357" t="s">
         <v>377</v>
       </c>
@@ -10366,7 +10344,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="358" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:18">
       <c r="A358" t="s">
         <v>378</v>
       </c>
@@ -10374,7 +10352,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="359" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:18">
       <c r="A359" t="s">
         <v>379</v>
       </c>
@@ -10383,7 +10361,7 @@
       </c>
       <c r="R359" s="1"/>
     </row>
-    <row r="360" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:18">
       <c r="A360" t="s">
         <v>380</v>
       </c>
@@ -10392,7 +10370,7 @@
       </c>
       <c r="R360" s="1"/>
     </row>
-    <row r="361" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:18">
       <c r="A361" t="s">
         <v>381</v>
       </c>
@@ -10401,7 +10379,7 @@
       </c>
       <c r="R361" s="1"/>
     </row>
-    <row r="362" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:18">
       <c r="A362" t="s">
         <v>382</v>
       </c>
@@ -10409,7 +10387,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="363" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:18">
       <c r="A363" t="s">
         <v>383</v>
       </c>
@@ -10418,7 +10396,7 @@
       </c>
       <c r="R363" s="1"/>
     </row>
-    <row r="364" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:18">
       <c r="A364" t="s">
         <v>384</v>
       </c>
@@ -10427,7 +10405,7 @@
       </c>
       <c r="R364" s="1"/>
     </row>
-    <row r="365" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:18">
       <c r="A365" t="s">
         <v>385</v>
       </c>
@@ -10436,7 +10414,7 @@
       </c>
       <c r="R365" s="1"/>
     </row>
-    <row r="366" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:18">
       <c r="A366" t="s">
         <v>386</v>
       </c>
@@ -10445,7 +10423,7 @@
       </c>
       <c r="R366" s="1"/>
     </row>
-    <row r="367" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:18">
       <c r="A367" t="s">
         <v>387</v>
       </c>
@@ -10453,7 +10431,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="368" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:18">
       <c r="A368" t="s">
         <v>388</v>
       </c>
@@ -10461,7 +10439,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="369" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:18">
       <c r="A369" t="s">
         <v>389</v>
       </c>
@@ -10470,7 +10448,7 @@
       </c>
       <c r="R369" s="1"/>
     </row>
-    <row r="370" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:18">
       <c r="A370" t="s">
         <v>390</v>
       </c>
@@ -10479,7 +10457,7 @@
       </c>
       <c r="R370" s="1"/>
     </row>
-    <row r="371" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:18">
       <c r="A371" t="s">
         <v>391</v>
       </c>
@@ -10488,7 +10466,7 @@
       </c>
       <c r="R371" s="1"/>
     </row>
-    <row r="372" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:18">
       <c r="A372" t="s">
         <v>392</v>
       </c>
@@ -10497,7 +10475,7 @@
       </c>
       <c r="R372" s="1"/>
     </row>
-    <row r="373" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:18">
       <c r="A373" t="s">
         <v>393</v>
       </c>
@@ -10506,7 +10484,7 @@
       </c>
       <c r="R373" s="1"/>
     </row>
-    <row r="374" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:18">
       <c r="A374" t="s">
         <v>394</v>
       </c>
@@ -10515,7 +10493,7 @@
       </c>
       <c r="R374" s="1"/>
     </row>
-    <row r="375" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:18">
       <c r="A375" t="s">
         <v>395</v>
       </c>
@@ -10524,7 +10502,7 @@
       </c>
       <c r="R375" s="1"/>
     </row>
-    <row r="376" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:18">
       <c r="A376" t="s">
         <v>396</v>
       </c>
@@ -10533,7 +10511,7 @@
       </c>
       <c r="R376" s="1"/>
     </row>
-    <row r="377" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:18">
       <c r="A377" t="s">
         <v>397</v>
       </c>
@@ -10541,7 +10519,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="378" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:18">
       <c r="A378" t="s">
         <v>398</v>
       </c>
@@ -10550,7 +10528,7 @@
       </c>
       <c r="R378" s="1"/>
     </row>
-    <row r="379" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:18">
       <c r="A379" t="s">
         <v>399</v>
       </c>
@@ -10559,7 +10537,7 @@
       </c>
       <c r="R379" s="1"/>
     </row>
-    <row r="380" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:18">
       <c r="A380" t="s">
         <v>400</v>
       </c>
@@ -10567,7 +10545,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="381" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:18">
       <c r="A381" t="s">
         <v>401</v>
       </c>
@@ -10576,7 +10554,7 @@
       </c>
       <c r="R381" s="1"/>
     </row>
-    <row r="382" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:18">
       <c r="A382" t="s">
         <v>402</v>
       </c>
@@ -10584,7 +10562,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="383" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:18">
       <c r="A383" t="s">
         <v>403</v>
       </c>
@@ -10592,7 +10570,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="384" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:18">
       <c r="A384" t="s">
         <v>404</v>
       </c>
@@ -10600,7 +10578,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="385" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:18">
       <c r="A385" t="s">
         <v>405</v>
       </c>
@@ -10608,7 +10586,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="386" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:18">
       <c r="A386" t="s">
         <v>406</v>
       </c>
@@ -10616,7 +10594,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="387" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:18">
       <c r="A387" t="s">
         <v>407</v>
       </c>
@@ -10625,7 +10603,7 @@
       </c>
       <c r="R387" s="1"/>
     </row>
-    <row r="388" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:18">
       <c r="A388" t="s">
         <v>408</v>
       </c>
@@ -10634,7 +10612,7 @@
       </c>
       <c r="R388" s="1"/>
     </row>
-    <row r="389" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:18">
       <c r="A389" t="s">
         <v>409</v>
       </c>
@@ -10643,7 +10621,7 @@
       </c>
       <c r="R389" s="1"/>
     </row>
-    <row r="390" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:18">
       <c r="A390" t="s">
         <v>410</v>
       </c>
@@ -10652,7 +10630,7 @@
       </c>
       <c r="R390" s="1"/>
     </row>
-    <row r="391" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:18">
       <c r="A391" t="s">
         <v>411</v>
       </c>
@@ -10660,7 +10638,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="392" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:18">
       <c r="A392" t="s">
         <v>412</v>
       </c>
@@ -10668,7 +10646,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="393" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:18">
       <c r="A393" t="s">
         <v>413</v>
       </c>
@@ -10676,7 +10654,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="394" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:18">
       <c r="A394" t="s">
         <v>414</v>
       </c>
@@ -10684,7 +10662,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="395" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:18">
       <c r="A395" t="s">
         <v>415</v>
       </c>
@@ -10693,7 +10671,7 @@
       </c>
       <c r="R395" s="1"/>
     </row>
-    <row r="396" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:18">
       <c r="A396" t="s">
         <v>416</v>
       </c>
@@ -10702,7 +10680,7 @@
       </c>
       <c r="R396" s="1"/>
     </row>
-    <row r="397" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:18">
       <c r="A397" t="s">
         <v>417</v>
       </c>
@@ -10710,7 +10688,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="398" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:18">
       <c r="A398" t="s">
         <v>418</v>
       </c>
@@ -10718,7 +10696,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="399" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:18">
       <c r="A399" t="s">
         <v>419</v>
       </c>
@@ -10727,7 +10705,7 @@
       </c>
       <c r="R399" s="1"/>
     </row>
-    <row r="400" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:18">
       <c r="A400" t="s">
         <v>420</v>
       </c>
@@ -10736,7 +10714,7 @@
       </c>
       <c r="R400" s="1"/>
     </row>
-    <row r="401" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:18">
       <c r="A401" t="s">
         <v>421</v>
       </c>
@@ -10745,7 +10723,7 @@
       </c>
       <c r="R401" s="1"/>
     </row>
-    <row r="402" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:18">
       <c r="A402" t="s">
         <v>422</v>
       </c>
@@ -10754,7 +10732,7 @@
       </c>
       <c r="R402" s="1"/>
     </row>
-    <row r="403" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:18">
       <c r="A403" t="s">
         <v>423</v>
       </c>
@@ -10763,7 +10741,7 @@
       </c>
       <c r="R403" s="1"/>
     </row>
-    <row r="404" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:18">
       <c r="A404" t="s">
         <v>424</v>
       </c>
@@ -10772,7 +10750,7 @@
       </c>
       <c r="R404" s="1"/>
     </row>
-    <row r="405" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:18">
       <c r="A405" t="s">
         <v>425</v>
       </c>
@@ -10781,7 +10759,7 @@
       </c>
       <c r="R405" s="1"/>
     </row>
-    <row r="406" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:18">
       <c r="A406" t="s">
         <v>426</v>
       </c>
@@ -10790,7 +10768,7 @@
       </c>
       <c r="R406" s="1"/>
     </row>
-    <row r="407" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:18">
       <c r="A407" t="s">
         <v>427</v>
       </c>
@@ -10799,7 +10777,7 @@
       </c>
       <c r="R407" s="1"/>
     </row>
-    <row r="408" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:18">
       <c r="A408" t="s">
         <v>428</v>
       </c>
@@ -10808,7 +10786,7 @@
       </c>
       <c r="R408" s="1"/>
     </row>
-    <row r="409" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:18">
       <c r="A409" t="s">
         <v>429</v>
       </c>
@@ -10817,7 +10795,7 @@
       </c>
       <c r="R409" s="1"/>
     </row>
-    <row r="410" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:18">
       <c r="A410" t="s">
         <v>430</v>
       </c>
@@ -10826,7 +10804,7 @@
       </c>
       <c r="R410" s="1"/>
     </row>
-    <row r="411" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:18">
       <c r="A411" t="s">
         <v>431</v>
       </c>
@@ -10835,7 +10813,7 @@
       </c>
       <c r="R411" s="1"/>
     </row>
-    <row r="412" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:18">
       <c r="A412" t="s">
         <v>432</v>
       </c>
@@ -10844,7 +10822,7 @@
       </c>
       <c r="R412" s="1"/>
     </row>
-    <row r="413" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:18">
       <c r="A413" t="s">
         <v>433</v>
       </c>
@@ -10853,7 +10831,7 @@
       </c>
       <c r="R413" s="1"/>
     </row>
-    <row r="414" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:18">
       <c r="A414" t="s">
         <v>434</v>
       </c>
@@ -10862,7 +10840,7 @@
       </c>
       <c r="R414" s="1"/>
     </row>
-    <row r="415" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:18">
       <c r="A415" t="s">
         <v>435</v>
       </c>
@@ -10871,7 +10849,7 @@
       </c>
       <c r="R415" s="1"/>
     </row>
-    <row r="416" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:18">
       <c r="A416" t="s">
         <v>436</v>
       </c>
@@ -10880,7 +10858,7 @@
       </c>
       <c r="R416" s="1"/>
     </row>
-    <row r="417" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:18">
       <c r="A417" t="s">
         <v>437</v>
       </c>
@@ -10889,7 +10867,7 @@
       </c>
       <c r="R417" s="1"/>
     </row>
-    <row r="418" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:18">
       <c r="A418" t="s">
         <v>438</v>
       </c>
@@ -10897,7 +10875,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="419" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:18">
       <c r="A419" t="s">
         <v>439</v>
       </c>
@@ -10906,7 +10884,7 @@
       </c>
       <c r="R419" s="1"/>
     </row>
-    <row r="420" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:18">
       <c r="A420" t="s">
         <v>440</v>
       </c>
@@ -10915,7 +10893,7 @@
       </c>
       <c r="R420" s="1"/>
     </row>
-    <row r="421" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:18">
       <c r="A421" t="s">
         <v>441</v>
       </c>
@@ -10924,7 +10902,7 @@
       </c>
       <c r="R421" s="1"/>
     </row>
-    <row r="422" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:18">
       <c r="A422" t="s">
         <v>442</v>
       </c>
@@ -10933,7 +10911,7 @@
       </c>
       <c r="R422" s="1"/>
     </row>
-    <row r="423" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:18">
       <c r="A423" t="s">
         <v>443</v>
       </c>
@@ -10942,7 +10920,7 @@
       </c>
       <c r="R423" s="1"/>
     </row>
-    <row r="424" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:18">
       <c r="A424" t="s">
         <v>444</v>
       </c>
@@ -10951,7 +10929,7 @@
       </c>
       <c r="R424" s="1"/>
     </row>
-    <row r="425" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:18">
       <c r="A425" t="s">
         <v>445</v>
       </c>
@@ -10960,7 +10938,7 @@
       </c>
       <c r="R425" s="1"/>
     </row>
-    <row r="426" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:18">
       <c r="A426" t="s">
         <v>446</v>
       </c>
@@ -10969,7 +10947,7 @@
       </c>
       <c r="R426" s="1"/>
     </row>
-    <row r="427" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:18">
       <c r="A427" t="s">
         <v>447</v>
       </c>
@@ -10978,7 +10956,7 @@
       </c>
       <c r="R427" s="1"/>
     </row>
-    <row r="428" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:18">
       <c r="A428" t="s">
         <v>448</v>
       </c>
@@ -10987,7 +10965,7 @@
       </c>
       <c r="R428" s="1"/>
     </row>
-    <row r="429" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:18">
       <c r="A429" t="s">
         <v>449</v>
       </c>
@@ -10996,7 +10974,7 @@
       </c>
       <c r="R429" s="1"/>
     </row>
-    <row r="430" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:18">
       <c r="A430" t="s">
         <v>450</v>
       </c>
@@ -11005,7 +10983,7 @@
       </c>
       <c r="R430" s="1"/>
     </row>
-    <row r="431" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:18">
       <c r="A431" t="s">
         <v>451</v>
       </c>
@@ -11014,7 +10992,7 @@
       </c>
       <c r="R431" s="1"/>
     </row>
-    <row r="432" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:18">
       <c r="A432" t="s">
         <v>452</v>
       </c>
@@ -11023,7 +11001,7 @@
       </c>
       <c r="R432" s="1"/>
     </row>
-    <row r="433" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:18">
       <c r="A433" t="s">
         <v>453</v>
       </c>
@@ -11031,7 +11009,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="434" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:18">
       <c r="A434" t="s">
         <v>454</v>
       </c>
@@ -11039,7 +11017,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="435" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:18">
       <c r="A435" t="s">
         <v>455</v>
       </c>
@@ -11048,7 +11026,7 @@
       </c>
       <c r="R435" s="1"/>
     </row>
-    <row r="436" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:18">
       <c r="A436" t="s">
         <v>456</v>
       </c>
@@ -11057,7 +11035,7 @@
       </c>
       <c r="R436" s="1"/>
     </row>
-    <row r="437" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:18">
       <c r="A437" t="s">
         <v>457</v>
       </c>
@@ -11066,7 +11044,7 @@
       </c>
       <c r="R437" s="1"/>
     </row>
-    <row r="438" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:18">
       <c r="A438" t="s">
         <v>458</v>
       </c>
@@ -11075,7 +11053,7 @@
       </c>
       <c r="R438" s="1"/>
     </row>
-    <row r="439" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:18">
       <c r="A439" t="s">
         <v>459</v>
       </c>
@@ -11084,7 +11062,7 @@
       </c>
       <c r="R439" s="1"/>
     </row>
-    <row r="440" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:18">
       <c r="A440" t="s">
         <v>460</v>
       </c>
@@ -11093,7 +11071,7 @@
       </c>
       <c r="R440" s="1"/>
     </row>
-    <row r="441" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:18">
       <c r="A441" t="s">
         <v>461</v>
       </c>
@@ -11102,7 +11080,7 @@
       </c>
       <c r="R441" s="1"/>
     </row>
-    <row r="442" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:18">
       <c r="A442" t="s">
         <v>462</v>
       </c>
@@ -11111,7 +11089,7 @@
       </c>
       <c r="R442" s="1"/>
     </row>
-    <row r="443" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:18">
       <c r="A443" t="s">
         <v>463</v>
       </c>
@@ -11120,7 +11098,7 @@
       </c>
       <c r="R443" s="1"/>
     </row>
-    <row r="444" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:18">
       <c r="A444" t="s">
         <v>464</v>
       </c>
@@ -11128,7 +11106,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="445" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:18">
       <c r="A445" t="s">
         <v>465</v>
       </c>
@@ -11137,7 +11115,7 @@
       </c>
       <c r="R445" s="1"/>
     </row>
-    <row r="446" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:18">
       <c r="A446" t="s">
         <v>466</v>
       </c>
@@ -11146,7 +11124,7 @@
       </c>
       <c r="R446" s="1"/>
     </row>
-    <row r="447" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:18">
       <c r="A447" t="s">
         <v>467</v>
       </c>
@@ -11154,7 +11132,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="448" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:18">
       <c r="A448" t="s">
         <v>468</v>
       </c>
@@ -11163,7 +11141,7 @@
       </c>
       <c r="R448" s="1"/>
     </row>
-    <row r="449" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:18">
       <c r="A449" t="s">
         <v>469</v>
       </c>
@@ -11172,7 +11150,7 @@
       </c>
       <c r="R449" s="1"/>
     </row>
-    <row r="450" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:18">
       <c r="A450" t="s">
         <v>470</v>
       </c>
@@ -11181,7 +11159,7 @@
       </c>
       <c r="R450" s="1"/>
     </row>
-    <row r="451" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:18">
       <c r="A451" t="s">
         <v>471</v>
       </c>
@@ -11190,7 +11168,7 @@
       </c>
       <c r="R451" s="1"/>
     </row>
-    <row r="452" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:18">
       <c r="A452" t="s">
         <v>472</v>
       </c>
@@ -11199,7 +11177,7 @@
       </c>
       <c r="R452" s="1"/>
     </row>
-    <row r="453" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:18">
       <c r="A453" t="s">
         <v>473</v>
       </c>
@@ -11208,7 +11186,7 @@
       </c>
       <c r="R453" s="1"/>
     </row>
-    <row r="454" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:18">
       <c r="A454" t="s">
         <v>474</v>
       </c>
@@ -11217,7 +11195,7 @@
       </c>
       <c r="R454" s="1"/>
     </row>
-    <row r="455" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:18">
       <c r="A455" t="s">
         <v>475</v>
       </c>
@@ -11226,7 +11204,7 @@
       </c>
       <c r="R455" s="1"/>
     </row>
-    <row r="456" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:18">
       <c r="A456" t="s">
         <v>476</v>
       </c>
@@ -11234,7 +11212,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="457" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:18">
       <c r="A457" t="s">
         <v>477</v>
       </c>
@@ -11242,7 +11220,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="458" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:18">
       <c r="A458" t="s">
         <v>478</v>
       </c>
@@ -11251,7 +11229,7 @@
       </c>
       <c r="R458" s="1"/>
     </row>
-    <row r="459" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:18">
       <c r="A459" t="s">
         <v>479</v>
       </c>
@@ -11260,7 +11238,7 @@
       </c>
       <c r="R459" s="1"/>
     </row>
-    <row r="460" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:18">
       <c r="A460" t="s">
         <v>480</v>
       </c>
@@ -11269,7 +11247,7 @@
       </c>
       <c r="R460" s="1"/>
     </row>
-    <row r="461" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:18">
       <c r="A461" t="s">
         <v>481</v>
       </c>
@@ -11278,7 +11256,7 @@
       </c>
       <c r="R461" s="1"/>
     </row>
-    <row r="462" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:18">
       <c r="A462" t="s">
         <v>482</v>
       </c>
@@ -11286,7 +11264,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="463" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:18">
       <c r="A463" t="s">
         <v>483</v>
       </c>
@@ -11295,7 +11273,7 @@
       </c>
       <c r="R463" s="1"/>
     </row>
-    <row r="464" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:18">
       <c r="A464" t="s">
         <v>484</v>
       </c>
@@ -11304,7 +11282,7 @@
       </c>
       <c r="R464" s="1"/>
     </row>
-    <row r="465" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:18">
       <c r="A465" t="s">
         <v>485</v>
       </c>
@@ -11313,7 +11291,7 @@
       </c>
       <c r="R465" s="1"/>
     </row>
-    <row r="466" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:18">
       <c r="A466" t="s">
         <v>486</v>
       </c>
@@ -11322,7 +11300,7 @@
       </c>
       <c r="R466" s="1"/>
     </row>
-    <row r="467" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:18">
       <c r="A467" t="s">
         <v>487</v>
       </c>
@@ -11331,7 +11309,7 @@
       </c>
       <c r="R467" s="1"/>
     </row>
-    <row r="468" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:18">
       <c r="A468" t="s">
         <v>488</v>
       </c>
@@ -11340,7 +11318,7 @@
       </c>
       <c r="R468" s="1"/>
     </row>
-    <row r="469" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:18">
       <c r="A469" t="s">
         <v>489</v>
       </c>
@@ -11348,7 +11326,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="470" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:18">
       <c r="A470" t="s">
         <v>490</v>
       </c>
@@ -11356,7 +11334,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="471" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:18">
       <c r="A471" t="s">
         <v>491</v>
       </c>
@@ -11364,7 +11342,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="472" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:18">
       <c r="A472" t="s">
         <v>492</v>
       </c>
@@ -11372,7 +11350,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="473" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:18">
       <c r="A473" t="s">
         <v>493</v>
       </c>
@@ -11380,7 +11358,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="474" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:18">
       <c r="A474" t="s">
         <v>494</v>
       </c>
@@ -11389,7 +11367,7 @@
       </c>
       <c r="R474" s="1"/>
     </row>
-    <row r="475" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:18">
       <c r="A475" t="s">
         <v>495</v>
       </c>
@@ -11398,7 +11376,7 @@
       </c>
       <c r="R475" s="1"/>
     </row>
-    <row r="476" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:18">
       <c r="A476" t="s">
         <v>496</v>
       </c>
@@ -11406,7 +11384,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="477" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:18">
       <c r="A477" t="s">
         <v>497</v>
       </c>
@@ -11414,7 +11392,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="478" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:18">
       <c r="A478" t="s">
         <v>498</v>
       </c>
@@ -11422,7 +11400,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="479" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:18">
       <c r="A479" t="s">
         <v>499</v>
       </c>
@@ -11430,7 +11408,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="480" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:18">
       <c r="A480" t="s">
         <v>500</v>
       </c>
@@ -11439,7 +11417,7 @@
       </c>
       <c r="R480" s="1"/>
     </row>
-    <row r="481" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:18">
       <c r="A481" t="s">
         <v>501</v>
       </c>
@@ -11448,7 +11426,7 @@
       </c>
       <c r="R481" s="1"/>
     </row>
-    <row r="482" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:18">
       <c r="A482" t="s">
         <v>502</v>
       </c>
@@ -11457,7 +11435,7 @@
       </c>
       <c r="R482" s="1"/>
     </row>
-    <row r="483" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:18">
       <c r="A483" t="s">
         <v>503</v>
       </c>
@@ -11466,7 +11444,7 @@
       </c>
       <c r="R483" s="1"/>
     </row>
-    <row r="484" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:18">
       <c r="A484" t="s">
         <v>504</v>
       </c>
@@ -11474,7 +11452,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="485" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:18">
       <c r="A485" t="s">
         <v>505</v>
       </c>
@@ -11483,7 +11461,7 @@
       </c>
       <c r="R485" s="1"/>
     </row>
-    <row r="486" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:18">
       <c r="A486" t="s">
         <v>506</v>
       </c>
@@ -11492,7 +11470,7 @@
       </c>
       <c r="R486" s="1"/>
     </row>
-    <row r="487" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:18">
       <c r="A487" t="s">
         <v>507</v>
       </c>
@@ -11501,7 +11479,7 @@
       </c>
       <c r="R487" s="1"/>
     </row>
-    <row r="488" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:18">
       <c r="A488" t="s">
         <v>508</v>
       </c>
@@ -11510,7 +11488,7 @@
       </c>
       <c r="R488" s="1"/>
     </row>
-    <row r="489" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:18">
       <c r="A489" t="s">
         <v>509</v>
       </c>
@@ -11519,7 +11497,7 @@
       </c>
       <c r="R489" s="1"/>
     </row>
-    <row r="490" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:18">
       <c r="A490" t="s">
         <v>510</v>
       </c>
@@ -11527,7 +11505,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="491" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:18">
       <c r="A491" t="s">
         <v>511</v>
       </c>
@@ -11536,7 +11514,7 @@
       </c>
       <c r="R491" s="1"/>
     </row>
-    <row r="492" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:18">
       <c r="A492" t="s">
         <v>512</v>
       </c>
@@ -11545,7 +11523,7 @@
       </c>
       <c r="R492" s="1"/>
     </row>
-    <row r="493" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:18">
       <c r="A493" t="s">
         <v>513</v>
       </c>
@@ -11554,7 +11532,7 @@
       </c>
       <c r="R493" s="1"/>
     </row>
-    <row r="494" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:18">
       <c r="A494" t="s">
         <v>514</v>
       </c>
@@ -11563,7 +11541,7 @@
       </c>
       <c r="R494" s="1"/>
     </row>
-    <row r="495" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:18">
       <c r="A495" t="s">
         <v>515</v>
       </c>
@@ -11572,7 +11550,7 @@
       </c>
       <c r="R495" s="1"/>
     </row>
-    <row r="496" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:18">
       <c r="A496" t="s">
         <v>516</v>
       </c>
@@ -11580,7 +11558,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="497" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:18">
       <c r="A497" t="s">
         <v>517</v>
       </c>
@@ -11589,7 +11567,7 @@
       </c>
       <c r="R497" s="1"/>
     </row>
-    <row r="498" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:18">
       <c r="A498" t="s">
         <v>518</v>
       </c>
@@ -11598,7 +11576,7 @@
       </c>
       <c r="R498" s="1"/>
     </row>
-    <row r="499" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:18">
       <c r="A499" t="s">
         <v>519</v>
       </c>
@@ -11607,7 +11585,7 @@
       </c>
       <c r="R499" s="1"/>
     </row>
-    <row r="500" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:18">
       <c r="A500" t="s">
         <v>520</v>
       </c>
@@ -11615,7 +11593,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="501" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:18">
       <c r="A501" t="s">
         <v>521</v>
       </c>
@@ -11624,7 +11602,7 @@
       </c>
       <c r="R501" s="1"/>
     </row>
-    <row r="502" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:18">
       <c r="A502" t="s">
         <v>522</v>
       </c>
@@ -11632,7 +11610,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="503" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:18">
       <c r="A503" t="s">
         <v>523</v>
       </c>
@@ -11640,7 +11618,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="504" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:18">
       <c r="A504" t="s">
         <v>524</v>
       </c>
@@ -11649,7 +11627,7 @@
       </c>
       <c r="R504" s="1"/>
     </row>
-    <row r="505" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:18">
       <c r="A505" t="s">
         <v>525</v>
       </c>
@@ -11657,7 +11635,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="506" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:18">
       <c r="A506" t="s">
         <v>526</v>
       </c>
@@ -11665,7 +11643,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="507" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:18">
       <c r="A507" t="s">
         <v>527</v>
       </c>
@@ -11674,7 +11652,7 @@
       </c>
       <c r="R507" s="1"/>
     </row>
-    <row r="508" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:18">
       <c r="A508" t="s">
         <v>528</v>
       </c>
@@ -11683,7 +11661,7 @@
       </c>
       <c r="R508" s="1"/>
     </row>
-    <row r="509" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:18">
       <c r="A509" t="s">
         <v>529</v>
       </c>
@@ -11691,7 +11669,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="510" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:18">
       <c r="A510" t="s">
         <v>530</v>
       </c>
@@ -11700,7 +11678,7 @@
       </c>
       <c r="R510" s="1"/>
     </row>
-    <row r="511" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:18">
       <c r="A511" t="s">
         <v>531</v>
       </c>
@@ -11709,7 +11687,7 @@
       </c>
       <c r="R511" s="1"/>
     </row>
-    <row r="512" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:18">
       <c r="A512" t="s">
         <v>532</v>
       </c>
@@ -11718,7 +11696,7 @@
       </c>
       <c r="R512" s="1"/>
     </row>
-    <row r="513" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:18">
       <c r="A513" t="s">
         <v>533</v>
       </c>
@@ -11727,7 +11705,7 @@
       </c>
       <c r="R513" s="1"/>
     </row>
-    <row r="514" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:18">
       <c r="A514" t="s">
         <v>534</v>
       </c>
@@ -11735,7 +11713,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="515" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:18">
       <c r="A515" t="s">
         <v>535</v>
       </c>
@@ -11744,7 +11722,7 @@
       </c>
       <c r="R515" s="1"/>
     </row>
-    <row r="516" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:18">
       <c r="A516" t="s">
         <v>536</v>
       </c>
@@ -11753,7 +11731,7 @@
       </c>
       <c r="R516" s="1"/>
     </row>
-    <row r="517" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:18">
       <c r="A517" t="s">
         <v>537</v>
       </c>
@@ -11761,7 +11739,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="518" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:18">
       <c r="A518" t="s">
         <v>538</v>
       </c>
@@ -11770,7 +11748,7 @@
       </c>
       <c r="R518" s="1"/>
     </row>
-    <row r="519" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:18">
       <c r="A519" t="s">
         <v>539</v>
       </c>
@@ -11779,7 +11757,7 @@
       </c>
       <c r="R519" s="1"/>
     </row>
-    <row r="520" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:18">
       <c r="A520" t="s">
         <v>540</v>
       </c>
@@ -11788,7 +11766,7 @@
       </c>
       <c r="R520" s="1"/>
     </row>
-    <row r="521" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:18">
       <c r="A521" t="s">
         <v>541</v>
       </c>
@@ -11797,7 +11775,7 @@
       </c>
       <c r="R521" s="1"/>
     </row>
-    <row r="522" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:18">
       <c r="A522" t="s">
         <v>542</v>
       </c>
@@ -11806,7 +11784,7 @@
       </c>
       <c r="R522" s="1"/>
     </row>
-    <row r="523" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:18">
       <c r="A523" t="s">
         <v>543</v>
       </c>
@@ -11815,7 +11793,7 @@
       </c>
       <c r="R523" s="1"/>
     </row>
-    <row r="524" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:18">
       <c r="A524" t="s">
         <v>544</v>
       </c>
@@ -11824,7 +11802,7 @@
       </c>
       <c r="R524" s="1"/>
     </row>
-    <row r="525" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:18">
       <c r="A525" t="s">
         <v>545</v>
       </c>
@@ -11833,7 +11811,7 @@
       </c>
       <c r="R525" s="1"/>
     </row>
-    <row r="526" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:18">
       <c r="A526" t="s">
         <v>546</v>
       </c>
@@ -11842,7 +11820,7 @@
       </c>
       <c r="R526" s="1"/>
     </row>
-    <row r="527" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:18">
       <c r="A527" t="s">
         <v>547</v>
       </c>
@@ -11850,7 +11828,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="528" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:18">
       <c r="A528" t="s">
         <v>548</v>
       </c>
@@ -11859,7 +11837,7 @@
       </c>
       <c r="R528" s="1"/>
     </row>
-    <row r="529" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:18">
       <c r="A529" t="s">
         <v>549</v>
       </c>
@@ -11868,7 +11846,7 @@
       </c>
       <c r="R529" s="1"/>
     </row>
-    <row r="530" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:18">
       <c r="A530" t="s">
         <v>550</v>
       </c>
@@ -11877,7 +11855,7 @@
       </c>
       <c r="R530" s="1"/>
     </row>
-    <row r="531" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:18">
       <c r="A531" t="s">
         <v>551</v>
       </c>
@@ -11886,7 +11864,7 @@
       </c>
       <c r="R531" s="1"/>
     </row>
-    <row r="532" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:18">
       <c r="A532" t="s">
         <v>552</v>
       </c>
@@ -11895,7 +11873,7 @@
       </c>
       <c r="R532" s="1"/>
     </row>
-    <row r="533" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:18">
       <c r="A533" t="s">
         <v>553</v>
       </c>
@@ -11904,7 +11882,7 @@
       </c>
       <c r="R533" s="1"/>
     </row>
-    <row r="534" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:18">
       <c r="A534" t="s">
         <v>554</v>
       </c>
@@ -11913,7 +11891,7 @@
       </c>
       <c r="R534" s="1"/>
     </row>
-    <row r="535" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:18">
       <c r="A535" t="s">
         <v>555</v>
       </c>
@@ -11922,7 +11900,7 @@
       </c>
       <c r="R535" s="1"/>
     </row>
-    <row r="536" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:18">
       <c r="A536" t="s">
         <v>556</v>
       </c>
@@ -11931,7 +11909,7 @@
       </c>
       <c r="R536" s="1"/>
     </row>
-    <row r="537" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:18">
       <c r="A537" t="s">
         <v>557</v>
       </c>
@@ -11940,7 +11918,7 @@
       </c>
       <c r="R537" s="1"/>
     </row>
-    <row r="538" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:18">
       <c r="A538" t="s">
         <v>558</v>
       </c>
@@ -11949,7 +11927,7 @@
       </c>
       <c r="R538" s="1"/>
     </row>
-    <row r="539" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:18">
       <c r="A539" t="s">
         <v>559</v>
       </c>
@@ -11957,7 +11935,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="540" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:18">
       <c r="A540" t="s">
         <v>560</v>
       </c>
@@ -11966,7 +11944,7 @@
       </c>
       <c r="R540" s="1"/>
     </row>
-    <row r="541" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:18">
       <c r="A541" t="s">
         <v>561</v>
       </c>
@@ -11975,7 +11953,7 @@
       </c>
       <c r="R541" s="1"/>
     </row>
-    <row r="542" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:18">
       <c r="A542" t="s">
         <v>562</v>
       </c>
@@ -11984,7 +11962,7 @@
       </c>
       <c r="R542" s="1"/>
     </row>
-    <row r="543" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:18">
       <c r="A543" t="s">
         <v>563</v>
       </c>
@@ -11993,7 +11971,7 @@
       </c>
       <c r="R543" s="1"/>
     </row>
-    <row r="544" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:18">
       <c r="A544" t="s">
         <v>564</v>
       </c>
@@ -12002,7 +11980,7 @@
       </c>
       <c r="R544" s="1"/>
     </row>
-    <row r="545" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:18">
       <c r="A545" t="s">
         <v>565</v>
       </c>
@@ -12011,7 +11989,7 @@
       </c>
       <c r="R545" s="1"/>
     </row>
-    <row r="546" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:18">
       <c r="A546" t="s">
         <v>566</v>
       </c>
@@ -12020,7 +11998,7 @@
       </c>
       <c r="R546" s="1"/>
     </row>
-    <row r="547" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:18">
       <c r="A547" t="s">
         <v>567</v>
       </c>
@@ -12029,7 +12007,7 @@
       </c>
       <c r="R547" s="1"/>
     </row>
-    <row r="548" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:18">
       <c r="A548" t="s">
         <v>568</v>
       </c>
@@ -12038,7 +12016,7 @@
       </c>
       <c r="R548" s="1"/>
     </row>
-    <row r="549" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:18">
       <c r="A549" t="s">
         <v>569</v>
       </c>
@@ -12047,7 +12025,7 @@
       </c>
       <c r="R549" s="1"/>
     </row>
-    <row r="550" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:18">
       <c r="A550" t="s">
         <v>570</v>
       </c>
@@ -12056,7 +12034,7 @@
       </c>
       <c r="R550" s="1"/>
     </row>
-    <row r="551" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:18">
       <c r="A551" t="s">
         <v>571</v>
       </c>
@@ -12065,7 +12043,7 @@
       </c>
       <c r="R551" s="1"/>
     </row>
-    <row r="552" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:18">
       <c r="A552" t="s">
         <v>572</v>
       </c>
@@ -12074,7 +12052,7 @@
       </c>
       <c r="R552" s="1"/>
     </row>
-    <row r="553" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:18">
       <c r="A553" t="s">
         <v>573</v>
       </c>
@@ -12083,7 +12061,7 @@
       </c>
       <c r="R553" s="1"/>
     </row>
-    <row r="554" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:18">
       <c r="A554" t="s">
         <v>574</v>
       </c>
@@ -12092,7 +12070,7 @@
       </c>
       <c r="R554" s="1"/>
     </row>
-    <row r="555" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:18">
       <c r="A555" t="s">
         <v>575</v>
       </c>
@@ -12101,7 +12079,7 @@
       </c>
       <c r="R555" s="1"/>
     </row>
-    <row r="556" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:18">
       <c r="A556" t="s">
         <v>576</v>
       </c>
@@ -12110,7 +12088,7 @@
       </c>
       <c r="R556" s="1"/>
     </row>
-    <row r="557" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:18">
       <c r="A557" t="s">
         <v>577</v>
       </c>
@@ -12119,7 +12097,7 @@
       </c>
       <c r="R557" s="1"/>
     </row>
-    <row r="558" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:18">
       <c r="A558" t="s">
         <v>578</v>
       </c>
@@ -12128,7 +12106,7 @@
       </c>
       <c r="R558" s="1"/>
     </row>
-    <row r="559" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:18">
       <c r="A559" t="s">
         <v>579</v>
       </c>
@@ -12137,7 +12115,7 @@
       </c>
       <c r="R559" s="1"/>
     </row>
-    <row r="560" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:18">
       <c r="A560" t="s">
         <v>580</v>
       </c>
@@ -12146,7 +12124,7 @@
       </c>
       <c r="R560" s="1"/>
     </row>
-    <row r="561" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:18">
       <c r="A561" t="s">
         <v>581</v>
       </c>
@@ -12155,7 +12133,7 @@
       </c>
       <c r="R561" s="1"/>
     </row>
-    <row r="562" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:18">
       <c r="A562" t="s">
         <v>582</v>
       </c>
@@ -12163,7 +12141,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="563" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:18">
       <c r="A563" t="s">
         <v>583</v>
       </c>
@@ -12172,7 +12150,7 @@
       </c>
       <c r="R563" s="1"/>
     </row>
-    <row r="564" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:18">
       <c r="A564" t="s">
         <v>584</v>
       </c>
@@ -12180,7 +12158,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="565" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:18">
       <c r="A565" t="s">
         <v>585</v>
       </c>
@@ -12188,7 +12166,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="566" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:18">
       <c r="A566" t="s">
         <v>586</v>
       </c>
@@ -12197,7 +12175,7 @@
       </c>
       <c r="R566" s="1"/>
     </row>
-    <row r="567" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:18">
       <c r="A567" t="s">
         <v>587</v>
       </c>
@@ -12206,7 +12184,7 @@
       </c>
       <c r="R567" s="1"/>
     </row>
-    <row r="568" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:18">
       <c r="A568" t="s">
         <v>588</v>
       </c>
@@ -12215,7 +12193,7 @@
       </c>
       <c r="R568" s="1"/>
     </row>
-    <row r="569" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:18">
       <c r="A569" t="s">
         <v>589</v>
       </c>
@@ -12224,7 +12202,7 @@
       </c>
       <c r="R569" s="1"/>
     </row>
-    <row r="570" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:18">
       <c r="A570" t="s">
         <v>590</v>
       </c>
@@ -12232,7 +12210,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="571" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:18">
       <c r="A571" t="s">
         <v>591</v>
       </c>
@@ -12241,7 +12219,7 @@
       </c>
       <c r="R571" s="1"/>
     </row>
-    <row r="572" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:18">
       <c r="A572" t="s">
         <v>592</v>
       </c>
@@ -12250,7 +12228,7 @@
       </c>
       <c r="R572" s="1"/>
     </row>
-    <row r="573" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:18">
       <c r="A573" t="s">
         <v>593</v>
       </c>
@@ -12259,7 +12237,7 @@
       </c>
       <c r="R573" s="1"/>
     </row>
-    <row r="574" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:18">
       <c r="A574" t="s">
         <v>594</v>
       </c>
@@ -12268,7 +12246,7 @@
       </c>
       <c r="R574" s="1"/>
     </row>
-    <row r="575" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:18">
       <c r="A575" t="s">
         <v>595</v>
       </c>
@@ -12276,7 +12254,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="576" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:18">
       <c r="A576" t="s">
         <v>596</v>
       </c>
@@ -12285,7 +12263,7 @@
       </c>
       <c r="R576" s="1"/>
     </row>
-    <row r="577" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:18">
       <c r="A577" t="s">
         <v>597</v>
       </c>
@@ -12293,7 +12271,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="578" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:18">
       <c r="A578" t="s">
         <v>598</v>
       </c>
@@ -12302,7 +12280,7 @@
       </c>
       <c r="R578" s="1"/>
     </row>
-    <row r="579" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:18">
       <c r="A579" t="s">
         <v>599</v>
       </c>
@@ -12310,7 +12288,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="580" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:18">
       <c r="A580" t="s">
         <v>600</v>
       </c>
@@ -12318,7 +12296,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="581" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:18">
       <c r="A581" t="s">
         <v>601</v>
       </c>
@@ -12326,7 +12304,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="582" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:18">
       <c r="A582" t="s">
         <v>602</v>
       </c>
@@ -12334,7 +12312,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="583" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:18">
       <c r="A583" t="s">
         <v>603</v>
       </c>
@@ -12342,7 +12320,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="584" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:18">
       <c r="A584" t="s">
         <v>604</v>
       </c>
@@ -12351,7 +12329,7 @@
       </c>
       <c r="R584" s="1"/>
     </row>
-    <row r="585" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:18">
       <c r="A585" t="s">
         <v>605</v>
       </c>
@@ -12360,7 +12338,7 @@
       </c>
       <c r="R585" s="1"/>
     </row>
-    <row r="586" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:18">
       <c r="A586" t="s">
         <v>606</v>
       </c>
@@ -12369,7 +12347,7 @@
       </c>
       <c r="R586" s="1"/>
     </row>
-    <row r="587" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:18">
       <c r="A587" t="s">
         <v>607</v>
       </c>
@@ -12378,7 +12356,7 @@
       </c>
       <c r="R587" s="1"/>
     </row>
-    <row r="588" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:18">
       <c r="A588" t="s">
         <v>608</v>
       </c>
@@ -12386,7 +12364,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="589" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:18">
       <c r="A589" t="s">
         <v>609</v>
       </c>
@@ -12394,7 +12372,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="590" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:18">
       <c r="A590" t="s">
         <v>610</v>
       </c>
@@ -12402,7 +12380,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="591" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:18">
       <c r="A591" t="s">
         <v>611</v>
       </c>
@@ -12410,7 +12388,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="592" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:18">
       <c r="A592" t="s">
         <v>612</v>
       </c>
@@ -12419,7 +12397,7 @@
       </c>
       <c r="R592" s="1"/>
     </row>
-    <row r="593" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:18">
       <c r="A593" t="s">
         <v>613</v>
       </c>
@@ -12428,7 +12406,7 @@
       </c>
       <c r="R593" s="1"/>
     </row>
-    <row r="594" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:18">
       <c r="A594" t="s">
         <v>614</v>
       </c>
@@ -12436,7 +12414,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="595" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:18">
       <c r="A595" t="s">
         <v>615</v>
       </c>
@@ -12445,7 +12423,7 @@
       </c>
       <c r="R595" s="1"/>
     </row>
-    <row r="596" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:18">
       <c r="A596" t="s">
         <v>616</v>
       </c>
@@ -12454,7 +12432,7 @@
       </c>
       <c r="R596" s="1"/>
     </row>
-    <row r="597" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:18">
       <c r="A597" t="s">
         <v>617</v>
       </c>
@@ -12462,7 +12440,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="598" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:18">
       <c r="A598" t="s">
         <v>618</v>
       </c>
@@ -12470,7 +12448,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="599" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:18">
       <c r="A599" t="s">
         <v>619</v>
       </c>
@@ -12479,7 +12457,7 @@
       </c>
       <c r="R599" s="1"/>
     </row>
-    <row r="600" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:18">
       <c r="A600" t="s">
         <v>620</v>
       </c>
@@ -12488,7 +12466,7 @@
       </c>
       <c r="R600" s="1"/>
     </row>
-    <row r="601" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:18">
       <c r="A601" t="s">
         <v>621</v>
       </c>
@@ -12497,7 +12475,7 @@
       </c>
       <c r="R601" s="1"/>
     </row>
-    <row r="602" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:18">
       <c r="A602" t="s">
         <v>622</v>
       </c>
@@ -12505,7 +12483,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="603" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:18">
       <c r="A603" t="s">
         <v>623</v>
       </c>
@@ -12513,7 +12491,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="604" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:18">
       <c r="A604" t="s">
         <v>624</v>
       </c>
@@ -12521,7 +12499,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="605" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:18">
       <c r="A605" t="s">
         <v>625</v>
       </c>
@@ -12529,7 +12507,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="606" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:18">
       <c r="A606" t="s">
         <v>626</v>
       </c>
@@ -12538,7 +12516,7 @@
       </c>
       <c r="R606" s="1"/>
     </row>
-    <row r="607" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:18">
       <c r="A607" t="s">
         <v>627</v>
       </c>
@@ -12546,7 +12524,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="608" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:18">
       <c r="A608" t="s">
         <v>628</v>
       </c>
@@ -12554,7 +12532,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="609" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:18">
       <c r="A609" t="s">
         <v>629</v>
       </c>
@@ -12563,7 +12541,7 @@
       </c>
       <c r="R609" s="1"/>
     </row>
-    <row r="610" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:18">
       <c r="A610" t="s">
         <v>630</v>
       </c>
@@ -12572,7 +12550,7 @@
       </c>
       <c r="R610" s="1"/>
     </row>
-    <row r="611" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:18">
       <c r="A611" t="s">
         <v>631</v>
       </c>
@@ -12581,7 +12559,7 @@
       </c>
       <c r="R611" s="1"/>
     </row>
-    <row r="612" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:18">
       <c r="A612" t="s">
         <v>632</v>
       </c>
@@ -12590,7 +12568,7 @@
       </c>
       <c r="R612" s="1"/>
     </row>
-    <row r="613" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:18">
       <c r="A613" t="s">
         <v>633</v>
       </c>
@@ -12599,7 +12577,7 @@
       </c>
       <c r="R613" s="1"/>
     </row>
-    <row r="614" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:18">
       <c r="A614" t="s">
         <v>634</v>
       </c>
@@ -12608,7 +12586,7 @@
       </c>
       <c r="R614" s="1"/>
     </row>
-    <row r="615" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:18">
       <c r="A615" t="s">
         <v>635</v>
       </c>
@@ -12617,7 +12595,7 @@
       </c>
       <c r="R615" s="1"/>
     </row>
-    <row r="616" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:18">
       <c r="A616" t="s">
         <v>636</v>
       </c>
@@ -12626,7 +12604,7 @@
       </c>
       <c r="R616" s="1"/>
     </row>
-    <row r="617" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:18">
       <c r="A617" t="s">
         <v>637</v>
       </c>
@@ -12635,7 +12613,7 @@
       </c>
       <c r="R617" s="1"/>
     </row>
-    <row r="618" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:18">
       <c r="A618" t="s">
         <v>638</v>
       </c>
@@ -12644,7 +12622,7 @@
       </c>
       <c r="R618" s="1"/>
     </row>
-    <row r="619" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:18">
       <c r="A619" t="s">
         <v>639</v>
       </c>
@@ -12653,7 +12631,7 @@
       </c>
       <c r="R619" s="1"/>
     </row>
-    <row r="620" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="620" spans="1:18">
       <c r="A620" t="s">
         <v>640</v>
       </c>
@@ -12662,7 +12640,7 @@
       </c>
       <c r="R620" s="1"/>
     </row>
-    <row r="621" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:18">
       <c r="A621" t="s">
         <v>641</v>
       </c>
@@ -12671,7 +12649,7 @@
       </c>
       <c r="R621" s="1"/>
     </row>
-    <row r="622" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:18">
       <c r="A622" t="s">
         <v>642</v>
       </c>
@@ -12679,7 +12657,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="623" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:18">
       <c r="A623" t="s">
         <v>643</v>
       </c>
@@ -12687,7 +12665,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="624" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:18">
       <c r="A624" t="s">
         <v>644</v>
       </c>
@@ -12695,7 +12673,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:13">
       <c r="A625" t="s">
         <v>645</v>
       </c>
@@ -12703,7 +12681,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:13">
       <c r="A626" t="s">
         <v>646</v>
       </c>
@@ -12711,7 +12689,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:13">
       <c r="A627" t="s">
         <v>647</v>
       </c>
@@ -12719,7 +12697,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:13">
       <c r="A628" t="s">
         <v>648</v>
       </c>
@@ -12727,7 +12705,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:13">
       <c r="A629" t="s">
         <v>649</v>
       </c>
@@ -12735,7 +12713,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:13">
       <c r="A630" t="s">
         <v>650</v>
       </c>
@@ -12743,7 +12721,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:13">
       <c r="A631" t="s">
         <v>651</v>
       </c>
@@ -12751,7 +12729,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:13">
       <c r="A632" t="s">
         <v>652</v>
       </c>
@@ -12759,7 +12737,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:13">
       <c r="A633" t="s">
         <v>653</v>
       </c>
@@ -12767,7 +12745,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:13">
       <c r="A634" t="s">
         <v>654</v>
       </c>
@@ -12775,7 +12753,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:13">
       <c r="A635" t="s">
         <v>655</v>
       </c>
@@ -12783,7 +12761,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:13">
       <c r="A636" t="s">
         <v>656</v>
       </c>
@@ -12791,7 +12769,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:13">
       <c r="A637" t="s">
         <v>657</v>
       </c>
@@ -12799,7 +12777,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:13">
       <c r="A638" t="s">
         <v>658</v>
       </c>
@@ -12807,7 +12785,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:13">
       <c r="A639" t="s">
         <v>659</v>
       </c>
@@ -12815,7 +12793,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:13">
       <c r="A640" t="s">
         <v>660</v>
       </c>
@@ -12823,7 +12801,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="641" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:18">
       <c r="A641" t="s">
         <v>661</v>
       </c>
@@ -12831,7 +12809,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="642" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:18">
       <c r="A642" t="s">
         <v>662</v>
       </c>
@@ -12839,7 +12817,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="643" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:18">
       <c r="A643" t="s">
         <v>663</v>
       </c>
@@ -12848,7 +12826,7 @@
       </c>
       <c r="R643" s="1"/>
     </row>
-    <row r="644" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:18">
       <c r="A644" t="s">
         <v>664</v>
       </c>
@@ -12856,7 +12834,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="645" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:18">
       <c r="A645" t="s">
         <v>665</v>
       </c>
@@ -12865,7 +12843,7 @@
       </c>
       <c r="R645" s="1"/>
     </row>
-    <row r="646" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:18">
       <c r="A646" t="s">
         <v>666</v>
       </c>
@@ -12874,7 +12852,7 @@
       </c>
       <c r="R646" s="1"/>
     </row>
-    <row r="647" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:18">
       <c r="A647" t="s">
         <v>667</v>
       </c>
@@ -12883,7 +12861,7 @@
       </c>
       <c r="R647" s="1"/>
     </row>
-    <row r="648" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:18">
       <c r="A648" t="s">
         <v>668</v>
       </c>
@@ -12892,7 +12870,7 @@
       </c>
       <c r="R648" s="1"/>
     </row>
-    <row r="649" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:18">
       <c r="A649" t="s">
         <v>669</v>
       </c>
@@ -12900,7 +12878,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="650" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:18">
       <c r="A650" t="s">
         <v>670</v>
       </c>
@@ -12909,7 +12887,7 @@
       </c>
       <c r="R650" s="1"/>
     </row>
-    <row r="651" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:18">
       <c r="A651" t="s">
         <v>671</v>
       </c>
@@ -12918,7 +12896,7 @@
       </c>
       <c r="R651" s="1"/>
     </row>
-    <row r="652" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:18">
       <c r="A652" t="s">
         <v>672</v>
       </c>
@@ -12927,7 +12905,7 @@
       </c>
       <c r="R652" s="1"/>
     </row>
-    <row r="653" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:18">
       <c r="A653" t="s">
         <v>673</v>
       </c>
@@ -12936,7 +12914,7 @@
       </c>
       <c r="R653" s="1"/>
     </row>
-    <row r="654" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:18">
       <c r="A654" t="s">
         <v>674</v>
       </c>
@@ -12944,7 +12922,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="655" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:18">
       <c r="A655" t="s">
         <v>675</v>
       </c>
@@ -12953,7 +12931,7 @@
       </c>
       <c r="R655" s="1"/>
     </row>
-    <row r="656" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:18">
       <c r="A656" t="s">
         <v>676</v>
       </c>
@@ -12961,7 +12939,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="657" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:18">
       <c r="A657" t="s">
         <v>677</v>
       </c>
@@ -12969,7 +12947,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="658" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:18">
       <c r="A658" t="s">
         <v>678</v>
       </c>
@@ -12978,7 +12956,7 @@
       </c>
       <c r="R658" s="1"/>
     </row>
-    <row r="659" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:18">
       <c r="A659" t="s">
         <v>679</v>
       </c>
@@ -12987,7 +12965,7 @@
       </c>
       <c r="R659" s="1"/>
     </row>
-    <row r="660" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:18">
       <c r="A660" t="s">
         <v>680</v>
       </c>
@@ -12996,7 +12974,7 @@
       </c>
       <c r="R660" s="1"/>
     </row>
-    <row r="661" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:18">
       <c r="A661" t="s">
         <v>681</v>
       </c>
@@ -13004,7 +12982,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="662" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:18">
       <c r="A662" t="s">
         <v>682</v>
       </c>
@@ -13013,7 +12991,7 @@
       </c>
       <c r="R662" s="1"/>
     </row>
-    <row r="663" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:18">
       <c r="A663" t="s">
         <v>683</v>
       </c>
@@ -13022,7 +13000,7 @@
       </c>
       <c r="R663" s="1"/>
     </row>
-    <row r="664" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:18">
       <c r="A664" t="s">
         <v>684</v>
       </c>
@@ -13031,7 +13009,7 @@
       </c>
       <c r="R664" s="1"/>
     </row>
-    <row r="665" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:18">
       <c r="A665" t="s">
         <v>685</v>
       </c>
@@ -13040,7 +13018,7 @@
       </c>
       <c r="R665" s="1"/>
     </row>
-    <row r="666" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:18">
       <c r="A666" t="s">
         <v>686</v>
       </c>
@@ -13048,7 +13026,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="667" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:18">
       <c r="A667" t="s">
         <v>687</v>
       </c>
@@ -13056,7 +13034,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="668" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:18">
       <c r="A668" t="s">
         <v>688</v>
       </c>
@@ -13064,7 +13042,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="669" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:18">
       <c r="A669" t="s">
         <v>689</v>
       </c>
@@ -13073,7 +13051,7 @@
       </c>
       <c r="R669" s="1"/>
     </row>
-    <row r="670" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:18">
       <c r="A670" t="s">
         <v>690</v>
       </c>
@@ -13082,7 +13060,7 @@
       </c>
       <c r="R670" s="1"/>
     </row>
-    <row r="671" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:18">
       <c r="A671" t="s">
         <v>691</v>
       </c>
@@ -13091,7 +13069,7 @@
       </c>
       <c r="R671" s="1"/>
     </row>
-    <row r="672" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:18">
       <c r="A672" t="s">
         <v>692</v>
       </c>
@@ -13099,7 +13077,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="673" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:18">
       <c r="A673" t="s">
         <v>693</v>
       </c>
@@ -13108,7 +13086,7 @@
       </c>
       <c r="R673" s="1"/>
     </row>
-    <row r="674" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:18">
       <c r="A674" t="s">
         <v>694</v>
       </c>
@@ -13117,7 +13095,7 @@
       </c>
       <c r="R674" s="1"/>
     </row>
-    <row r="675" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:18">
       <c r="A675" t="s">
         <v>695</v>
       </c>
@@ -13126,7 +13104,7 @@
       </c>
       <c r="R675" s="1"/>
     </row>
-    <row r="676" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:18">
       <c r="A676" t="s">
         <v>696</v>
       </c>
@@ -13135,7 +13113,7 @@
       </c>
       <c r="R676" s="1"/>
     </row>
-    <row r="677" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:18">
       <c r="A677" t="s">
         <v>697</v>
       </c>
@@ -13143,7 +13121,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="678" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:18">
       <c r="A678" t="s">
         <v>698</v>
       </c>
@@ -13151,7 +13129,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="679" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:18">
       <c r="A679" t="s">
         <v>699</v>
       </c>
@@ -13159,7 +13137,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="680" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:18">
       <c r="A680" t="s">
         <v>700</v>
       </c>
@@ -13167,7 +13145,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="681" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="681" spans="1:18">
       <c r="A681" t="s">
         <v>701</v>
       </c>
@@ -13175,7 +13153,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="682" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:18">
       <c r="A682" t="s">
         <v>702</v>
       </c>
@@ -13183,7 +13161,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="683" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:18">
       <c r="A683" t="s">
         <v>703</v>
       </c>
@@ -13191,7 +13169,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="684" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:18">
       <c r="A684" t="s">
         <v>704</v>
       </c>
@@ -13199,7 +13177,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="685" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:18">
       <c r="A685" t="s">
         <v>705</v>
       </c>
@@ -13207,7 +13185,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="686" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:18">
       <c r="A686" t="s">
         <v>706</v>
       </c>
@@ -13215,7 +13193,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="687" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:18">
       <c r="A687" t="s">
         <v>707</v>
       </c>
@@ -13224,7 +13202,7 @@
       </c>
       <c r="R687" s="1"/>
     </row>
-    <row r="688" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:18">
       <c r="A688" t="s">
         <v>708</v>
       </c>
@@ -13233,7 +13211,7 @@
       </c>
       <c r="R688" s="1"/>
     </row>
-    <row r="689" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:18">
       <c r="A689" t="s">
         <v>709</v>
       </c>
@@ -13242,7 +13220,7 @@
       </c>
       <c r="R689" s="1"/>
     </row>
-    <row r="690" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="690" spans="1:18">
       <c r="A690" t="s">
         <v>710</v>
       </c>
@@ -13251,7 +13229,7 @@
       </c>
       <c r="R690" s="1"/>
     </row>
-    <row r="691" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:18">
       <c r="A691" t="s">
         <v>711</v>
       </c>
@@ -13260,7 +13238,7 @@
       </c>
       <c r="R691" s="1"/>
     </row>
-    <row r="692" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:18">
       <c r="A692" t="s">
         <v>712</v>
       </c>
@@ -13269,7 +13247,7 @@
       </c>
       <c r="R692" s="1"/>
     </row>
-    <row r="693" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:18">
       <c r="A693" t="s">
         <v>713</v>
       </c>
@@ -13278,7 +13256,7 @@
       </c>
       <c r="R693" s="1"/>
     </row>
-    <row r="694" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="694" spans="1:18">
       <c r="A694" t="s">
         <v>714</v>
       </c>
@@ -13287,7 +13265,7 @@
       </c>
       <c r="R694" s="1"/>
     </row>
-    <row r="695" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="695" spans="1:18">
       <c r="A695" t="s">
         <v>715</v>
       </c>
@@ -13296,7 +13274,7 @@
       </c>
       <c r="R695" s="1"/>
     </row>
-    <row r="696" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:18">
       <c r="A696" t="s">
         <v>716</v>
       </c>
@@ -13305,7 +13283,7 @@
       </c>
       <c r="R696" s="1"/>
     </row>
-    <row r="697" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:18">
       <c r="A697" t="s">
         <v>717</v>
       </c>
@@ -13314,7 +13292,7 @@
       </c>
       <c r="R697" s="1"/>
     </row>
-    <row r="698" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:18">
       <c r="A698" t="s">
         <v>718</v>
       </c>
@@ -13322,7 +13300,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="699" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="699" spans="1:18">
       <c r="A699" t="s">
         <v>719</v>
       </c>
@@ -13331,7 +13309,7 @@
       </c>
       <c r="R699" s="1"/>
     </row>
-    <row r="700" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="700" spans="1:18">
       <c r="A700" t="s">
         <v>720</v>
       </c>
@@ -13340,7 +13318,7 @@
       </c>
       <c r="R700" s="1"/>
     </row>
-    <row r="701" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="701" spans="1:18">
       <c r="A701" t="s">
         <v>721</v>
       </c>
@@ -13349,7 +13327,7 @@
       </c>
       <c r="R701" s="1"/>
     </row>
-    <row r="702" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="702" spans="1:18">
       <c r="A702" t="s">
         <v>722</v>
       </c>
@@ -13357,7 +13335,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="703" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="703" spans="1:18">
       <c r="A703" t="s">
         <v>723</v>
       </c>
@@ -13366,7 +13344,7 @@
       </c>
       <c r="R703" s="1"/>
     </row>
-    <row r="704" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="704" spans="1:18">
       <c r="A704" t="s">
         <v>724</v>
       </c>
@@ -13375,7 +13353,7 @@
       </c>
       <c r="R704" s="1"/>
     </row>
-    <row r="705" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="705" spans="1:18">
       <c r="A705" t="s">
         <v>725</v>
       </c>
@@ -13384,517 +13362,517 @@
       </c>
       <c r="R705" s="1"/>
     </row>
-    <row r="706" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="706" spans="1:18">
       <c r="A706" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="707" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="707" spans="1:18">
       <c r="A707" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="708" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="708" spans="1:18">
       <c r="A708" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="709" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="709" spans="1:18">
       <c r="A709" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="710" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="710" spans="1:18">
       <c r="A710" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="711" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="711" spans="1:18">
       <c r="A711" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="712" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="712" spans="1:18">
       <c r="A712" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="713" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="713" spans="1:18">
       <c r="A713" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="714" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="714" spans="1:18">
       <c r="A714" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="715" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="715" spans="1:18">
       <c r="A715" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="716" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="716" spans="1:18">
       <c r="A716" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="717" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="717" spans="1:18">
       <c r="A717" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="718" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="718" spans="1:18">
       <c r="A718" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="719" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="719" spans="1:18">
       <c r="A719" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="720" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="720" spans="1:18">
       <c r="A720" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="721" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="721" spans="1:1">
       <c r="A721" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="722" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="722" spans="1:1">
       <c r="A722" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="723" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="723" spans="1:1">
       <c r="A723" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="724" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="724" spans="1:1">
       <c r="A724" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="725" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="725" spans="1:1">
       <c r="A725" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="726" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="726" spans="1:1">
       <c r="A726" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="727" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="727" spans="1:1">
       <c r="A727" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="728" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="728" spans="1:1">
       <c r="A728" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="729" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="729" spans="1:1">
       <c r="A729" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="730" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="730" spans="1:1">
       <c r="A730" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="731" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="731" spans="1:1">
       <c r="A731" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="732" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="732" spans="1:1">
       <c r="A732" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="733" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="733" spans="1:1">
       <c r="A733" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="734" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="734" spans="1:1">
       <c r="A734" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="735" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="735" spans="1:1">
       <c r="A735" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="736" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="736" spans="1:1">
       <c r="A736" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="737" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="737" spans="1:1">
       <c r="A737" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="738" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="738" spans="1:1">
       <c r="A738" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="739" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="739" spans="1:1">
       <c r="A739" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="740" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="740" spans="1:1">
       <c r="A740" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="741" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="741" spans="1:1">
       <c r="A741" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="742" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="742" spans="1:1">
       <c r="A742" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="743" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="743" spans="1:1">
       <c r="A743" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="744" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="744" spans="1:1">
       <c r="A744" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="745" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="745" spans="1:1">
       <c r="A745" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="746" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="746" spans="1:1">
       <c r="A746" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="747" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="747" spans="1:1">
       <c r="A747" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="748" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="748" spans="1:1">
       <c r="A748" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="749" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="749" spans="1:1">
       <c r="A749" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="750" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="750" spans="1:1">
       <c r="A750" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="751" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="751" spans="1:1">
       <c r="A751" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="752" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="752" spans="1:1">
       <c r="A752" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="753" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="753" spans="1:1">
       <c r="A753" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="754" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="754" spans="1:1">
       <c r="A754" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="755" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="755" spans="1:1">
       <c r="A755" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="756" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="756" spans="1:1">
       <c r="A756" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="757" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="757" spans="1:1">
       <c r="A757" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="758" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="758" spans="1:1">
       <c r="A758" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="759" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="759" spans="1:1">
       <c r="A759" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="760" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="760" spans="1:1">
       <c r="A760" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="761" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="761" spans="1:1">
       <c r="A761" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="762" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="762" spans="1:1">
       <c r="A762" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="763" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="763" spans="1:1">
       <c r="A763" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="764" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="764" spans="1:1">
       <c r="A764" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="765" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="765" spans="1:1">
       <c r="A765" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="766" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="766" spans="1:1">
       <c r="A766" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="767" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="767" spans="1:1">
       <c r="A767" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="768" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="768" spans="1:1">
       <c r="A768" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="769" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="769" spans="1:1">
       <c r="A769" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="770" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="770" spans="1:1">
       <c r="A770" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="771" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="771" spans="1:1">
       <c r="A771" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="772" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="772" spans="1:1">
       <c r="A772" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="773" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="773" spans="1:1">
       <c r="A773" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="774" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="774" spans="1:1">
       <c r="A774" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="775" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="775" spans="1:1">
       <c r="A775" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="776" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="776" spans="1:1">
       <c r="A776" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="777" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="777" spans="1:1">
       <c r="A777" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="778" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="778" spans="1:1">
       <c r="A778" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="779" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="779" spans="1:1">
       <c r="A779" t="s">
         <v>799</v>
       </c>
     </row>
-    <row r="780" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="780" spans="1:1">
       <c r="A780" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="781" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="781" spans="1:1">
       <c r="A781" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="782" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="782" spans="1:1">
       <c r="A782" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="783" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="783" spans="1:1">
       <c r="A783" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="784" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="784" spans="1:1">
       <c r="A784" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="785" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="785" spans="1:1">
       <c r="A785" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="786" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="786" spans="1:1">
       <c r="A786" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="787" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="787" spans="1:1">
       <c r="A787" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="788" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="788" spans="1:1">
       <c r="A788" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="789" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="789" spans="1:1">
       <c r="A789" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="790" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="790" spans="1:1">
       <c r="A790" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="791" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="791" spans="1:1">
       <c r="A791" t="s">
         <v>811</v>
       </c>
     </row>
-    <row r="792" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="792" spans="1:1">
       <c r="A792" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="793" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="793" spans="1:1">
       <c r="A793" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="794" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="794" spans="1:1">
       <c r="A794" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="795" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="795" spans="1:1">
       <c r="A795" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="796" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="796" spans="1:1">
       <c r="A796" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="797" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="797" spans="1:1">
       <c r="A797" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="798" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="798" spans="1:1">
       <c r="A798" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="799" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="799" spans="1:1">
       <c r="A799" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="800" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="800" spans="1:1">
       <c r="A800" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="801" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="801" spans="1:1">
       <c r="A801" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="802" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="802" spans="1:1">
       <c r="A802" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="803" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="803" spans="1:1">
       <c r="A803" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="804" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="804" spans="1:1">
       <c r="A804" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="805" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="805" spans="1:1">
       <c r="A805" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="806" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="806" spans="1:1">
       <c r="A806" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="807" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="807" spans="1:1">
       <c r="A807" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="808" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="808" spans="1:1">
       <c r="A808" t="s">
         <v>828</v>
       </c>
